--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\desofs2026-tue_crr_3\Documentation\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\desofs2026-tue_crr_3\Deliverables\Sprint_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0786169B-60A6-41A0-9BA4-6C7C0537F973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8656B3-B0BD-48D3-A8AC-C22E265C62C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="13" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="959">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2828,6 +2828,120 @@
   </si>
   <si>
     <t>Email address, postal addressare assigned a protection level that determines encryption on  logging.</t>
+  </si>
+  <si>
+    <t>Inputs is processed directly by strongly typed .NET models .Direct String inputs used for file names (`ReportName`) are canonicalized immediately upon receipt in `SanitizeFileName` by stripping directory separators and traversal sequences , and resolving to a safe filename using `Path.GetFileName`before operating on it</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L235</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L258</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database: The repository layer uses Entity Framework Core parameterized LINQ queries, delegating parameter escaping to the database provider itself.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Output escaping is performed as a final step during serialization via "EscapeCsvField", which escapes spreadsheet formula triggers and prevents CSV/Formula injection.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/TeaRepository.cs#L8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">he application does not manually construct JSON strings via concatenation.  API serialization is handled  by  .NET </t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/OrderController.cs#L11</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/OrderRepository.cs#L10</t>
+  </si>
+  <si>
+    <t>Repositories interact with the database through Entity Framework Core.This uses parameterized queries, ensuring that variables are sent as SQL parameters rather than concatenated SQL strings</t>
+  </si>
+  <si>
+    <t>Data passed to external interpreters or potentially risky contexts is parameterized or escaped beforehand. Relational database queries use EF Core parameterization, while CSV exports utilize the method `EscapeCsvField`</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/SessionRepository.cs</t>
+  </si>
+  <si>
+    <t>The application does not dynamically evaluate or compile format string templates using untrusted inputs. All string formatting throughout the codebase (such as in filename generation and CSV writing) relies on compile-time string interpolation ($) or hardcoded format strings</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L205</t>
+  </si>
+  <si>
+    <t>The application is built entirely in managed C#  which is a memory-safe language. There is no use of unsafe blocks or manual pointers</t>
+  </si>
+  <si>
+    <t>Input range validations are applied to numeric inputs (such as quantities and prices). Furthermore, financial calculations utilize the .NET 'decimal' data type, which natively throws an `OverflowException`</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderDTOs.cs#L7</t>
+  </si>
+  <si>
+    <t>Standard memory allocation is managed by the .NET Garbage Collector. Unmanaged system resources, such as stream writers and memory streams, are wrapped in standard 'using' statements ensuring guaranteed resource release immediately after use</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L212</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The application deserializes incoming API payloads strictly into defined, strongly typed C# DTOs using 'System.Text.Json'. It does not accept or deserialize arbitrary  types  and the use of of insecure serializers  is prohibited</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/OrderController.cs#L119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application utilizes positive validation (allow-listing). Incoming data is validated against strictly defined schemas and  strict numeric ranges </t>
+  </si>
+  <si>
+    <t>Validation rules are strictly enforced at the trusted server-side Application Service layer</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Combinations of related data items are validated for logical consistency on the server. For example, in sales report generation, the system validates that `StartDate` is chronologically earlier than or equal to `EndDate` before executing the database query</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L197</t>
+  </si>
+  <si>
+    <t>State transitions are validated sequentially in the domain layer. For example, an order cannot be transitioned to a 'Canceled' state unless its current sequential state permits it</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Domain/Orders/Order.cs#L42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logical business boundaries are strictly enforced. Standard users can only retrieve or cancel orders that match their authenticated  userId.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application utilizes the Unit of Work pattern to coordinate persistence across repositories. Business transactions are kept in-memory and committed atomically. </t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Domain/Orders/Order.cs#L39</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L38</t>
+  </si>
+  <si>
+    <t>The application implements standard anti-automation and resource protection controls using the built-in ASP.NET Core Rate Limiting middleware. This prevents automated scripts from triggering denial of service (DoS), resource exhaustion, or data scraping.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Security/RateLimiting.cs#L7</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/AuthController.cs#L28</t>
+  </si>
+  <si>
+    <t>The application prevents race conditions and over-allocation  using Optimistic Concurrency Control (OCC)</t>
+  </si>
+  <si>
+    <t>Fill after commit</t>
   </si>
 </sst>
 </file>
@@ -3301,10 +3415,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3485,10 +3599,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.42105263157894735</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3669,7 +3783,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.33333333333333331</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3850,10 +3964,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.36666666666666664</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.61538461538461542</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4519,41 +4633,41 @@
       </c>
       <c r="D6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" ref="E6:E20" si="0">IF(C6=0,"",D6/C6)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="4">
         <v>19</v>
       </c>
       <c r="G6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,2)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" ref="H6:H22" si="1">IF(F6=0,"",G6/F6)</f>
-        <v>0</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" ref="K6:K13" si="2">IF(I6=0,"",J6/I6)</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L6" s="4">
         <f>COUNTIF('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant")</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M22" si="3">IF(B6=0,"",L6/B6)</f>
-        <v>0</v>
+        <v>0.36666666666666664</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4568,22 +4682,22 @@
       </c>
       <c r="D7" s="7">
         <f>COUNTIFS('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant",'V2 - Validation and Business Lo'!$E$2:$E$18,1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="7">
         <v>7</v>
       </c>
       <c r="G7" s="7">
         <f>COUNTIFS('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant",'V2 - Validation and Business Lo'!$E$2:$E$18,2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I7" s="7">
         <v>2</v>
@@ -4598,11 +4712,11 @@
       </c>
       <c r="L7" s="7">
         <f>COUNTIF('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61538461538461542</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5348,11 +5462,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>8.7606837606837601E-2</v>
+        <v>0.15427350427350428</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5360,11 +5474,11 @@
       </c>
       <c r="G23" s="10">
         <f>SUM(G6:G22)</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H23" s="11">
         <f>IFERROR(AVERAGE(H6:H22),"")</f>
-        <v>2.4000509294626941E-2</v>
+        <v>9.0785117874901164E-2</v>
       </c>
       <c r="I23" s="10">
         <f>SUM(I6:I22)</f>
@@ -5372,19 +5486,19 @@
       </c>
       <c r="J23" s="10">
         <f>SUM(J6:J22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="11">
         <f>IFERROR(AVERAGE(K6:K22),"")</f>
-        <v>0</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>3.2645606265591778E-2</v>
+        <v>9.0413328739196608E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10227,10 +10341,14 @@
         <v>2</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -10249,10 +10367,14 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>925</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
@@ -10285,7 +10407,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -10307,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
@@ -10329,10 +10451,14 @@
         <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
@@ -10351,10 +10477,14 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>931</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
@@ -10373,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
@@ -10395,7 +10525,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
@@ -10417,7 +10547,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
@@ -10439,7 +10569,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -10461,7 +10591,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -10483,10 +10613,14 @@
         <v>3</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>926</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -10519,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
@@ -10541,7 +10675,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
@@ -10563,10 +10697,14 @@
         <v>2</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>932</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
@@ -10585,7 +10723,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
@@ -10607,7 +10745,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
@@ -10629,7 +10767,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
@@ -10651,7 +10789,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
@@ -10673,7 +10811,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
@@ -10695,7 +10833,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
@@ -10717,10 +10855,14 @@
         <v>2</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
@@ -10739,7 +10881,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
@@ -10761,7 +10903,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
@@ -10797,9 +10939,11 @@
         <v>2</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>936</v>
+      </c>
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -10819,10 +10963,14 @@
         <v>2</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>937</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
@@ -10841,10 +10989,14 @@
         <v>2</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
@@ -10877,7 +11029,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
@@ -10899,10 +11051,14 @@
         <v>2</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>941</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>942</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
@@ -10921,7 +11077,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -10944,6 +11100,16 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" location="L235" xr:uid="{A84892FB-9B9D-4523-9A7E-2DA48FCFCA1F}"/>
+    <hyperlink ref="H4" r:id="rId2" location="L8" xr:uid="{BCA6D288-8A4B-4A20-854D-994C10E48932}"/>
+    <hyperlink ref="H15" r:id="rId3" location="L258" xr:uid="{25DD70A4-00A4-4831-9049-70628FB5F38C}"/>
+    <hyperlink ref="H8" r:id="rId4" location="L11" xr:uid="{3B438980-FE39-4E81-B42B-2CC167323DC9}"/>
+    <hyperlink ref="H9" r:id="rId5" location="L10" xr:uid="{08CC7360-7339-4631-994D-0EB25FEAA689}"/>
+    <hyperlink ref="H32" r:id="rId6" location="L212" xr:uid="{E5DAB9EF-00BE-4435-A7C3-C2D3D103CCF6}"/>
+    <hyperlink ref="H19" r:id="rId7" xr:uid="{EA877C8B-DE1F-48BC-A5DF-EFCEF855CB16}"/>
+    <hyperlink ref="H31" r:id="rId8" location="L7" xr:uid="{79E4D5CA-BA87-4EF3-A1E7-91EA186E8A66}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -10951,7 +11117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -11101,10 +11267,14 @@
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>943</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
@@ -11123,10 +11293,14 @@
         <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>944</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
@@ -11145,10 +11319,14 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>946</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>947</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
@@ -11181,10 +11359,14 @@
         <v>1</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>948</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
@@ -11203,10 +11385,14 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>950</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
@@ -11225,10 +11411,14 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
@@ -11247,10 +11437,14 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>957</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
@@ -11269,7 +11463,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
@@ -11288,7 +11482,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>140</v>
       </c>
@@ -11305,12 +11499,19 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>954</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>955</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>140</v>
       </c>
@@ -11327,7 +11528,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
@@ -11350,6 +11551,15 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H8" r:id="rId1" location="L190" xr:uid="{598CAFA4-055B-4A86-9723-2701E48D6B5E}"/>
+    <hyperlink ref="H9" r:id="rId2" location="L197" xr:uid="{E7854916-D85D-4CE1-863D-0D2D57C64538}"/>
+    <hyperlink ref="H11" r:id="rId3" location="L42" xr:uid="{3FAE36F8-A7C4-4842-87C8-EDB25C1DDC8E}"/>
+    <hyperlink ref="H12" r:id="rId4" location="L39" xr:uid="{3EDD0CD1-7836-4B5E-A687-06AD31F95DBF}"/>
+    <hyperlink ref="H13" r:id="rId5" location="L38" xr:uid="{A91F97D6-FD86-4237-AEBD-473B19266593}"/>
+    <hyperlink ref="H17" r:id="rId6" location="L7" xr:uid="{D773793C-1794-4A22-8B98-45097F9F4EC2}"/>
+    <hyperlink ref="I17" r:id="rId7" location="L28" xr:uid="{937F3CFB-6A68-4930-B95F-B6AE300E54FD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\desofs2026-tue_crr_3\Documentation\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0786169B-60A6-41A0-9BA4-6C7C0537F973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85DB334-B03A-4C87-B5F6-2A37DF57900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="13" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="965">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2828,6 +2828,138 @@
   </si>
   <si>
     <t>Email address, postal addressare assigned a protection level that determines encryption on  logging.</t>
+  </si>
+  <si>
+    <t>Inputs is processed directly by strongly typed .NET models .Direct String inputs used for file names (`ReportName`) are canonicalized immediately upon receipt in `SanitizeFileName` by stripping directory separators and traversal sequences , and resolving to a safe filename using `Path.GetFileName`before operating on it</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L235</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L258</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database: The repository layer uses Entity Framework Core parameterized LINQ queries, delegating parameter escaping to the database provider itself.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Output escaping is performed as a final step during serialization via "EscapeCsvField", which escapes spreadsheet formula triggers and prevents CSV/Formula injection.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/TeaRepository.cs#L8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">he application does not manually construct JSON strings via concatenation.  API serialization is handled  by  .NET </t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/OrderController.cs#L11</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/OrderRepository.cs#L10</t>
+  </si>
+  <si>
+    <t>Repositories interact with the database through Entity Framework Core.This uses parameterized queries, ensuring that variables are sent as SQL parameters rather than concatenated SQL strings</t>
+  </si>
+  <si>
+    <t>Data passed to external interpreters or potentially risky contexts is parameterized or escaped beforehand. Relational database queries use EF Core parameterization, while CSV exports utilize the method `EscapeCsvField`</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Persistence/Repositories/SessionRepository.cs</t>
+  </si>
+  <si>
+    <t>The application does not dynamically evaluate or compile format string templates using untrusted inputs. All string formatting throughout the codebase (such as in filename generation and CSV writing) relies on compile-time string interpolation ($) or hardcoded format strings</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L205</t>
+  </si>
+  <si>
+    <t>The application is built entirely in managed C#  which is a memory-safe language. There is no use of unsafe blocks or manual pointers</t>
+  </si>
+  <si>
+    <t>Input range validations are applied to numeric inputs (such as quantities and prices). Furthermore, financial calculations utilize the .NET 'decimal' data type, which natively throws an `OverflowException`</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderDTOs.cs#L7</t>
+  </si>
+  <si>
+    <t>Standard memory allocation is managed by the .NET Garbage Collector. Unmanaged system resources, such as stream writers and memory streams, are wrapped in standard 'using' statements ensuring guaranteed resource release immediately after use</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L212</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The application deserializes incoming API payloads strictly into defined, strongly typed C# DTOs using 'System.Text.Json'. It does not accept or deserialize arbitrary  types  and the use of of insecure serializers  is prohibited</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/OrderController.cs#L119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application utilizes positive validation (allow-listing). Incoming data is validated against strictly defined schemas and  strict numeric ranges </t>
+  </si>
+  <si>
+    <t>Validation rules are strictly enforced at the trusted server-side Application Service layer</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Combinations of related data items are validated for logical consistency on the server. For example, in sales report generation, the system validates that `StartDate` is chronologically earlier than or equal to `EndDate` before executing the database query</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L197</t>
+  </si>
+  <si>
+    <t>State transitions are validated sequentially in the domain layer. For example, an order cannot be transitioned to a 'Canceled' state unless its current sequential state permits it</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Domain/Orders/Order.cs#L42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logical business boundaries are strictly enforced. Standard users can only retrieve or cancel orders that match their authenticated  userId.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application utilizes the Unit of Work pattern to coordinate persistence across repositories. Business transactions are kept in-memory and committed atomically. </t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Domain/Orders/Order.cs#L39</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Application/Orders/OrderService.cs#L38</t>
+  </si>
+  <si>
+    <t>The application implements standard anti-automation and resource protection controls using the built-in ASP.NET Core Rate Limiting middleware. This prevents automated scripts from triggering denial of service (DoS), resource exhaustion, or data scraping.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Infrastructure/Security/RateLimiting.cs#L7</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/ff5dce5c732d9649d8f6ac4460f32af19f100fe6/TeaShop/TeaShop/Presentation/AuthController.cs#L28</t>
+  </si>
+  <si>
+    <t>The application prevents race conditions and over-allocation  using Optimistic Concurrency Control (OCC)</t>
+  </si>
+  <si>
+    <t>Fill after commit</t>
+  </si>
+  <si>
+    <t>Input validation requirements are documented through functional requirements and validation rules. The specification defines expected constraints for user registration, authentication, inventory management, and order processing operations.</t>
+  </si>
+  <si>
+    <t>Requirements.md - FR-01, FR-02, FR-04, FR-06, FR-08, Section 3 (BR-01 to BR-06)</t>
+  </si>
+  <si>
+    <t>Business validation rules are documented for inventory management, stock allocation, order creation, order access control, and order cancellation. Logical consistency requirements between related business entities are explicitly defined.</t>
+  </si>
+  <si>
+    <t>Requirements.md - FR-06, FR-08, FR-09, FR-10, FR-11, Section 3 (BR-01 to BR-06)</t>
+  </si>
+  <si>
+    <t>Business constraints and validation requirements are documented, including inventory management rules, stock allocation controls, prevention of negative stock values, transaction integrity requirements, concurrency handling, financial accuracy constraints, and order state management.</t>
+  </si>
+  <si>
+    <t>Requirements.md - NFR-01, NFR-02, NFR-05, Section 3 (BR-01 to BR-06)</t>
   </si>
 </sst>
 </file>
@@ -3165,7 +3297,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3301,10 +3433,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3485,10 +3617,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.42105263157894735</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3669,7 +3801,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.33333333333333331</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3850,10 +3982,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.36666666666666664</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.84615384615384615</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4411,13 +4543,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -4437,7 +4569,7 @@
       <c r="O1" s="28"/>
       <c r="P1" s="28"/>
     </row>
-    <row r="2" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4455,7 +4587,7 @@
       <c r="O2" s="29"/>
       <c r="P2" s="29"/>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="30"/>
       <c r="B3" s="30"/>
       <c r="C3" s="1"/>
@@ -4466,7 +4598,7 @@
       <c r="M3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -4507,7 +4639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -4519,44 +4651,44 @@
       </c>
       <c r="D6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" ref="E6:E20" si="0">IF(C6=0,"",D6/C6)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="4">
         <v>19</v>
       </c>
       <c r="G6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,2)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" ref="H6:H22" si="1">IF(F6=0,"",G6/F6)</f>
-        <v>0</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
       </c>
       <c r="J6" s="4">
         <f>COUNTIFS('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant",'V1 - Encoding and Sanitization'!$E$2:$E$36,3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" ref="K6:K13" si="2">IF(I6=0,"",J6/I6)</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L6" s="4">
         <f>COUNTIF('V1 - Encoding and Sanitization'!$F$2:$F$36,"Compliant")</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M22" si="3">IF(B6=0,"",L6/B6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.36666666666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
@@ -4568,22 +4700,22 @@
       </c>
       <c r="D7" s="7">
         <f>COUNTIFS('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant",'V2 - Validation and Business Lo'!$E$2:$E$18,1)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7">
         <v>7</v>
       </c>
       <c r="G7" s="7">
         <f>COUNTIFS('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant",'V2 - Validation and Business Lo'!$E$2:$E$18,2)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="7">
         <v>2</v>
@@ -4598,14 +4730,14 @@
       </c>
       <c r="L7" s="7">
         <f>COUNTIF('V2 - Validation and Business Lo'!$F$2:$F$18,"Compliant")</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.84615384615384615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -4654,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -4703,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -4752,7 +4884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -4801,7 +4933,7 @@
         <v>0.14893617021276595</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -4850,7 +4982,7 @@
         <v>0.21052631578947367</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -4899,7 +5031,7 @@
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -4946,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -4995,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -5044,7 +5176,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>26</v>
       </c>
@@ -5093,7 +5225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -5142,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>28</v>
       </c>
@@ -5191,7 +5323,7 @@
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -5240,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
@@ -5287,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -5334,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -5348,11 +5480,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>8.7606837606837601E-2</v>
+        <v>0.17094017094017094</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5360,11 +5492,11 @@
       </c>
       <c r="G23" s="10">
         <f>SUM(G6:G22)</f>
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H23" s="11">
         <f>IFERROR(AVERAGE(H6:H22),"")</f>
-        <v>2.4000509294626941E-2</v>
+        <v>0.10759184056397678</v>
       </c>
       <c r="I23" s="10">
         <f>SUM(I6:I22)</f>
@@ -5372,19 +5504,19 @@
       </c>
       <c r="J23" s="10">
         <f>SUM(J6:J22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="11">
         <f>IFERROR(AVERAGE(K6:K22),"")</f>
-        <v>0</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>3.2645606265591778E-2</v>
+        <v>0.10398798937268075</v>
       </c>
     </row>
   </sheetData>
@@ -5450,7 +5582,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5462,7 +5594,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -5488,7 +5620,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>490</v>
       </c>
@@ -5502,7 +5634,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>490</v>
       </c>
@@ -5524,7 +5656,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>490</v>
       </c>
@@ -5546,7 +5678,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>490</v>
       </c>
@@ -5568,7 +5700,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>498</v>
       </c>
@@ -5582,7 +5714,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>498</v>
       </c>
@@ -5604,7 +5736,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>498</v>
       </c>
@@ -5626,7 +5758,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>498</v>
       </c>
@@ -5648,7 +5780,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>498</v>
       </c>
@@ -5696,7 +5828,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5708,7 +5840,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -5734,7 +5866,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>508</v>
       </c>
@@ -5748,7 +5880,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>508</v>
       </c>
@@ -5770,7 +5902,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>508</v>
       </c>
@@ -5792,7 +5924,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>514</v>
       </c>
@@ -5806,7 +5938,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>514</v>
       </c>
@@ -5828,7 +5960,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>514</v>
       </c>
@@ -5850,7 +5982,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>514</v>
       </c>
@@ -5872,7 +6004,7 @@
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>522</v>
       </c>
@@ -5886,7 +6018,7 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>522</v>
       </c>
@@ -5908,7 +6040,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>522</v>
       </c>
@@ -5930,7 +6062,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>522</v>
       </c>
@@ -5952,7 +6084,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>522</v>
       </c>
@@ -5974,7 +6106,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>522</v>
       </c>
@@ -5996,7 +6128,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>534</v>
       </c>
@@ -6010,7 +6142,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>534</v>
       </c>
@@ -6032,7 +6164,7 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>534</v>
       </c>
@@ -6054,7 +6186,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>534</v>
       </c>
@@ -6076,7 +6208,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>534</v>
       </c>
@@ -6098,7 +6230,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>534</v>
       </c>
@@ -6120,7 +6252,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>534</v>
       </c>
@@ -6142,7 +6274,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>534</v>
       </c>
@@ -6164,7 +6296,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>534</v>
       </c>
@@ -6186,7 +6318,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>534</v>
       </c>
@@ -6208,7 +6340,7 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>534</v>
       </c>
@@ -6230,7 +6362,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>534</v>
       </c>
@@ -6252,7 +6384,7 @@
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>534</v>
       </c>
@@ -6274,7 +6406,7 @@
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>534</v>
       </c>
@@ -6296,7 +6428,7 @@
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
         <v>534</v>
       </c>
@@ -6318,7 +6450,7 @@
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>534</v>
       </c>
@@ -6340,7 +6472,7 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
         <v>534</v>
       </c>
@@ -6362,7 +6494,7 @@
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>568</v>
       </c>
@@ -6376,7 +6508,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>568</v>
       </c>
@@ -6398,7 +6530,7 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
         <v>568</v>
       </c>
@@ -6420,7 +6552,7 @@
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>568</v>
       </c>
@@ -6442,7 +6574,7 @@
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="s">
         <v>568</v>
       </c>
@@ -6464,7 +6596,7 @@
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>568</v>
       </c>
@@ -6486,7 +6618,7 @@
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
         <v>580</v>
       </c>
@@ -6500,7 +6632,7 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>580</v>
       </c>
@@ -6522,7 +6654,7 @@
       <c r="G39" s="16"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="19" t="s">
         <v>580</v>
       </c>
@@ -6544,7 +6676,7 @@
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="13" t="s">
         <v>586</v>
       </c>
@@ -6558,7 +6690,7 @@
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
         <v>586</v>
       </c>
@@ -6580,7 +6712,7 @@
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="19" t="s">
         <v>586</v>
       </c>
@@ -6602,7 +6734,7 @@
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
     </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>586</v>
       </c>
@@ -6650,7 +6782,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -6662,7 +6794,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -6688,7 +6820,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>594</v>
       </c>
@@ -6702,7 +6834,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>594</v>
       </c>
@@ -6724,7 +6856,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>594</v>
       </c>
@@ -6746,7 +6878,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>594</v>
       </c>
@@ -6768,7 +6900,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>594</v>
       </c>
@@ -6790,7 +6922,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>604</v>
       </c>
@@ -6804,7 +6936,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>604</v>
       </c>
@@ -6826,7 +6958,7 @@
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>604</v>
       </c>
@@ -6848,7 +6980,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>604</v>
       </c>
@@ -6870,7 +7002,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>604</v>
       </c>
@@ -6892,7 +7024,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>604</v>
       </c>
@@ -6914,7 +7046,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>616</v>
       </c>
@@ -6928,7 +7060,7 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>616</v>
       </c>
@@ -6950,7 +7082,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
         <v>616</v>
       </c>
@@ -6972,7 +7104,7 @@
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>616</v>
       </c>
@@ -6994,7 +7126,7 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>616</v>
       </c>
@@ -7016,7 +7148,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>616</v>
       </c>
@@ -7038,7 +7170,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>628</v>
       </c>
@@ -7052,7 +7184,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>628</v>
       </c>
@@ -7078,7 +7210,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>628</v>
       </c>
@@ -7100,7 +7232,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>628</v>
       </c>
@@ -7122,7 +7254,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>628</v>
       </c>
@@ -7144,7 +7276,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>638</v>
       </c>
@@ -7158,7 +7290,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>638</v>
       </c>
@@ -7180,7 +7312,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>638</v>
       </c>
@@ -7202,7 +7334,7 @@
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
         <v>644</v>
       </c>
@@ -7216,7 +7348,7 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>644</v>
       </c>
@@ -7238,7 +7370,7 @@
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
         <v>644</v>
       </c>
@@ -7260,7 +7392,7 @@
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
         <v>650</v>
       </c>
@@ -7274,7 +7406,7 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>650</v>
       </c>
@@ -7296,7 +7428,7 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
         <v>650</v>
       </c>
@@ -7347,7 +7479,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -7359,7 +7491,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -7385,7 +7517,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>656</v>
       </c>
@@ -7399,7 +7531,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>656</v>
       </c>
@@ -7421,7 +7553,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>656</v>
       </c>
@@ -7443,7 +7575,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>656</v>
       </c>
@@ -7465,7 +7597,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>656</v>
       </c>
@@ -7487,7 +7619,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>656</v>
       </c>
@@ -7509,7 +7641,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>668</v>
       </c>
@@ -7523,7 +7655,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>668</v>
       </c>
@@ -7545,7 +7677,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>668</v>
       </c>
@@ -7567,7 +7699,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>674</v>
       </c>
@@ -7581,7 +7713,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>674</v>
       </c>
@@ -7603,7 +7735,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>674</v>
       </c>
@@ -7625,7 +7757,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>674</v>
       </c>
@@ -7647,7 +7779,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
         <v>674</v>
       </c>
@@ -7669,7 +7801,7 @@
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>674</v>
       </c>
@@ -7717,7 +7849,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -7729,7 +7861,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -7755,7 +7887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>686</v>
       </c>
@@ -7769,7 +7901,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>686</v>
       </c>
@@ -7791,7 +7923,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>686</v>
       </c>
@@ -7813,7 +7945,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>686</v>
       </c>
@@ -7835,7 +7967,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>686</v>
       </c>
@@ -7857,7 +7989,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>696</v>
       </c>
@@ -7871,7 +8003,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>696</v>
       </c>
@@ -7893,7 +8025,7 @@
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>696</v>
       </c>
@@ -7915,7 +8047,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>696</v>
       </c>
@@ -7937,7 +8069,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>696</v>
       </c>
@@ -7959,7 +8091,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>696</v>
       </c>
@@ -7981,7 +8113,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>696</v>
       </c>
@@ -8003,7 +8135,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>710</v>
       </c>
@@ -8017,7 +8149,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>710</v>
       </c>
@@ -8039,7 +8171,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>710</v>
       </c>
@@ -8061,7 +8193,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>710</v>
       </c>
@@ -8083,7 +8215,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>710</v>
       </c>
@@ -8105,7 +8237,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>720</v>
       </c>
@@ -8119,7 +8251,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>720</v>
       </c>
@@ -8141,7 +8273,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>720</v>
       </c>
@@ -8163,7 +8295,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>720</v>
       </c>
@@ -8185,7 +8317,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>720</v>
       </c>
@@ -8207,7 +8339,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>720</v>
       </c>
@@ -8229,7 +8361,7 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>720</v>
       </c>
@@ -8251,7 +8383,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>720</v>
       </c>
@@ -8299,7 +8431,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8311,7 +8443,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -8337,7 +8469,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>736</v>
       </c>
@@ -8351,7 +8483,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>736</v>
       </c>
@@ -8377,7 +8509,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>736</v>
       </c>
@@ -8399,7 +8531,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>742</v>
       </c>
@@ -8413,7 +8545,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>742</v>
       </c>
@@ -8435,7 +8567,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>742</v>
       </c>
@@ -8457,7 +8589,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>742</v>
       </c>
@@ -8479,7 +8611,7 @@
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>742</v>
       </c>
@@ -8501,7 +8633,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>742</v>
       </c>
@@ -8523,7 +8655,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>742</v>
       </c>
@@ -8545,7 +8677,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>742</v>
       </c>
@@ -8567,7 +8699,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>742</v>
       </c>
@@ -8589,7 +8721,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>760</v>
       </c>
@@ -8603,7 +8735,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>760</v>
       </c>
@@ -8625,7 +8757,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>760</v>
       </c>
@@ -8647,7 +8779,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>760</v>
       </c>
@@ -8698,7 +8830,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8710,7 +8842,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -8736,7 +8868,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>768</v>
       </c>
@@ -8750,7 +8882,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>768</v>
       </c>
@@ -8772,7 +8904,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>768</v>
       </c>
@@ -8794,7 +8926,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>768</v>
       </c>
@@ -8816,7 +8948,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>768</v>
       </c>
@@ -8838,7 +8970,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>768</v>
       </c>
@@ -8860,7 +8992,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>780</v>
       </c>
@@ -8874,7 +9006,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>780</v>
       </c>
@@ -8896,7 +9028,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>780</v>
       </c>
@@ -8918,7 +9050,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>780</v>
       </c>
@@ -8940,7 +9072,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>780</v>
       </c>
@@ -8962,7 +9094,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>780</v>
       </c>
@@ -8984,7 +9116,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>792</v>
       </c>
@@ -8998,7 +9130,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>792</v>
       </c>
@@ -9020,7 +9152,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>792</v>
       </c>
@@ -9042,7 +9174,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>792</v>
       </c>
@@ -9064,7 +9196,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>792</v>
       </c>
@@ -9086,7 +9218,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>792</v>
       </c>
@@ -9108,7 +9240,7 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
         <v>792</v>
       </c>
@@ -9130,7 +9262,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>792</v>
       </c>
@@ -9152,7 +9284,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
         <v>808</v>
       </c>
@@ -9166,7 +9298,7 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>808</v>
       </c>
@@ -9188,7 +9320,7 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
         <v>808</v>
       </c>
@@ -9210,7 +9342,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>808</v>
       </c>
@@ -9232,7 +9364,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>808</v>
       </c>
@@ -9280,7 +9412,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -9292,7 +9424,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -9318,7 +9450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>818</v>
       </c>
@@ -9332,7 +9464,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>818</v>
       </c>
@@ -9354,7 +9486,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>822</v>
       </c>
@@ -9368,7 +9500,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>822</v>
       </c>
@@ -9390,7 +9522,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>822</v>
       </c>
@@ -9412,7 +9544,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>822</v>
       </c>
@@ -9434,7 +9566,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>822</v>
       </c>
@@ -9456,7 +9588,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>822</v>
       </c>
@@ -9478,7 +9610,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>834</v>
       </c>
@@ -9492,7 +9624,7 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>834</v>
       </c>
@@ -9514,7 +9646,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>834</v>
       </c>
@@ -9536,7 +9668,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>834</v>
       </c>
@@ -9558,7 +9690,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>834</v>
       </c>
@@ -9580,7 +9712,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>844</v>
       </c>
@@ -9594,7 +9726,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>844</v>
       </c>
@@ -9616,7 +9748,7 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>844</v>
       </c>
@@ -9638,7 +9770,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>844</v>
       </c>
@@ -9660,7 +9792,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>852</v>
       </c>
@@ -9674,7 +9806,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>852</v>
       </c>
@@ -9696,7 +9828,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>852</v>
       </c>
@@ -9718,7 +9850,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>852</v>
       </c>
@@ -9740,7 +9872,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>852</v>
       </c>
@@ -9788,7 +9920,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -9800,7 +9932,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -9826,7 +9958,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>862</v>
       </c>
@@ -9840,7 +9972,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>862</v>
       </c>
@@ -9862,7 +9994,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>862</v>
       </c>
@@ -9884,7 +10016,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>868</v>
       </c>
@@ -9898,7 +10030,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>868</v>
       </c>
@@ -9920,7 +10052,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>868</v>
       </c>
@@ -9942,7 +10074,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>868</v>
       </c>
@@ -9964,7 +10096,7 @@
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>868</v>
       </c>
@@ -9986,7 +10118,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>868</v>
       </c>
@@ -10008,7 +10140,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>868</v>
       </c>
@@ -10030,7 +10162,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>868</v>
       </c>
@@ -10052,7 +10184,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>868</v>
       </c>
@@ -10074,7 +10206,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>886</v>
       </c>
@@ -10088,7 +10220,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>886</v>
       </c>
@@ -10110,7 +10242,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>886</v>
       </c>
@@ -10158,7 +10290,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -10170,7 +10302,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -10196,7 +10328,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>41</v>
       </c>
@@ -10210,7 +10342,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>41</v>
       </c>
@@ -10227,12 +10359,16 @@
         <v>2</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>41</v>
       </c>
@@ -10249,12 +10385,16 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>925</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -10268,7 +10408,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>48</v>
       </c>
@@ -10285,12 +10425,12 @@
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>48</v>
       </c>
@@ -10307,12 +10447,12 @@
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>48</v>
       </c>
@@ -10329,12 +10469,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>48</v>
       </c>
@@ -10351,12 +10495,16 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>931</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>48</v>
       </c>
@@ -10373,12 +10521,12 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>48</v>
       </c>
@@ -10395,12 +10543,12 @@
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>48</v>
       </c>
@@ -10417,12 +10565,12 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>48</v>
       </c>
@@ -10439,12 +10587,12 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>48</v>
       </c>
@@ -10461,12 +10609,12 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
         <v>48</v>
       </c>
@@ -10483,12 +10631,16 @@
         <v>3</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>926</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>70</v>
       </c>
@@ -10502,7 +10654,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>70</v>
       </c>
@@ -10519,12 +10671,12 @@
         <v>1</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>70</v>
       </c>
@@ -10541,12 +10693,12 @@
         <v>1</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -10563,12 +10715,16 @@
         <v>2</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>932</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
         <v>70</v>
       </c>
@@ -10585,12 +10741,12 @@
         <v>2</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -10607,12 +10763,12 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>70</v>
       </c>
@@ -10629,12 +10785,12 @@
         <v>2</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -10651,12 +10807,12 @@
         <v>2</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
         <v>70</v>
       </c>
@@ -10673,12 +10829,12 @@
         <v>2</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>70</v>
       </c>
@@ -10695,12 +10851,12 @@
         <v>2</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>70</v>
       </c>
@@ -10717,12 +10873,16 @@
         <v>2</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-    </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
         <v>70</v>
       </c>
@@ -10739,12 +10899,12 @@
         <v>2</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19" t="s">
         <v>70</v>
       </c>
@@ -10761,12 +10921,12 @@
         <v>3</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
         <v>96</v>
       </c>
@@ -10780,7 +10940,7 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>96</v>
       </c>
@@ -10797,12 +10957,14 @@
         <v>2</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>936</v>
+      </c>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
         <v>96</v>
       </c>
@@ -10819,12 +10981,16 @@
         <v>2</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>937</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
         <v>96</v>
       </c>
@@ -10841,12 +11007,16 @@
         <v>2</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-    </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="13" t="s">
         <v>104</v>
       </c>
@@ -10860,7 +11030,7 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
         <v>104</v>
       </c>
@@ -10877,12 +11047,12 @@
         <v>1</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="19" t="s">
         <v>104</v>
       </c>
@@ -10899,12 +11069,16 @@
         <v>2</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-    </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>941</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
         <v>104</v>
       </c>
@@ -10921,7 +11095,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -10944,6 +11118,16 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" location="L235" xr:uid="{A84892FB-9B9D-4523-9A7E-2DA48FCFCA1F}"/>
+    <hyperlink ref="H4" r:id="rId2" location="L8" xr:uid="{BCA6D288-8A4B-4A20-854D-994C10E48932}"/>
+    <hyperlink ref="H15" r:id="rId3" location="L258" xr:uid="{25DD70A4-00A4-4831-9049-70628FB5F38C}"/>
+    <hyperlink ref="H8" r:id="rId4" location="L11" xr:uid="{3B438980-FE39-4E81-B42B-2CC167323DC9}"/>
+    <hyperlink ref="H9" r:id="rId5" location="L10" xr:uid="{08CC7360-7339-4631-994D-0EB25FEAA689}"/>
+    <hyperlink ref="H32" r:id="rId6" location="L212" xr:uid="{E5DAB9EF-00BE-4435-A7C3-C2D3D103CCF6}"/>
+    <hyperlink ref="H19" r:id="rId7" xr:uid="{EA877C8B-DE1F-48BC-A5DF-EFCEF855CB16}"/>
+    <hyperlink ref="H31" r:id="rId8" location="L7" xr:uid="{79E4D5CA-BA87-4EF3-A1E7-91EA186E8A66}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -10951,8 +11135,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -10964,7 +11148,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -10990,7 +11174,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>112</v>
       </c>
@@ -11004,7 +11188,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>112</v>
       </c>
@@ -11021,12 +11205,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>959</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>112</v>
       </c>
@@ -11043,12 +11231,16 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>961</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>112</v>
       </c>
@@ -11065,12 +11257,16 @@
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>963</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>120</v>
       </c>
@@ -11084,7 +11280,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>120</v>
       </c>
@@ -11101,12 +11297,16 @@
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>943</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>120</v>
       </c>
@@ -11123,12 +11323,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>944</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>120</v>
       </c>
@@ -11145,12 +11349,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>946</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>128</v>
       </c>
@@ -11164,7 +11372,7 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>128</v>
       </c>
@@ -11181,12 +11389,16 @@
         <v>1</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>948</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>128</v>
       </c>
@@ -11203,12 +11415,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>950</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>128</v>
       </c>
@@ -11225,12 +11441,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>128</v>
       </c>
@@ -11247,12 +11467,16 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>957</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>128</v>
       </c>
@@ -11269,12 +11493,12 @@
         <v>3</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>140</v>
       </c>
@@ -11288,7 +11512,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>140</v>
       </c>
@@ -11305,12 +11529,19 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>954</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>955</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>140</v>
       </c>
@@ -11327,7 +11558,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
@@ -11350,6 +11581,15 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H8" r:id="rId1" location="L190" xr:uid="{598CAFA4-055B-4A86-9723-2701E48D6B5E}"/>
+    <hyperlink ref="H9" r:id="rId2" location="L197" xr:uid="{E7854916-D85D-4CE1-863D-0D2D57C64538}"/>
+    <hyperlink ref="H11" r:id="rId3" location="L42" xr:uid="{3FAE36F8-A7C4-4842-87C8-EDB25C1DDC8E}"/>
+    <hyperlink ref="H12" r:id="rId4" location="L39" xr:uid="{3EDD0CD1-7836-4B5E-A687-06AD31F95DBF}"/>
+    <hyperlink ref="H13" r:id="rId5" location="L38" xr:uid="{A91F97D6-FD86-4237-AEBD-473B19266593}"/>
+    <hyperlink ref="H17" r:id="rId6" location="L7" xr:uid="{D773793C-1794-4A22-8B98-45097F9F4EC2}"/>
+    <hyperlink ref="I17" r:id="rId7" location="L28" xr:uid="{937F3CFB-6A68-4930-B95F-B6AE300E54FD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -11358,7 +11598,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -11370,7 +11610,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -11396,7 +11636,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>146</v>
       </c>
@@ -11410,7 +11650,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
@@ -11432,7 +11672,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>150</v>
       </c>
@@ -11446,7 +11686,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>150</v>
       </c>
@@ -11468,7 +11708,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>150</v>
       </c>
@@ -11490,7 +11730,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>150</v>
       </c>
@@ -11512,7 +11752,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>158</v>
       </c>
@@ -11526,7 +11766,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>158</v>
       </c>
@@ -11548,7 +11788,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>158</v>
       </c>
@@ -11570,7 +11810,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>158</v>
       </c>
@@ -11592,7 +11832,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>158</v>
       </c>
@@ -11614,7 +11854,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>158</v>
       </c>
@@ -11636,7 +11876,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>170</v>
       </c>
@@ -11650,7 +11890,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>170</v>
       </c>
@@ -11672,7 +11912,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>170</v>
       </c>
@@ -11694,7 +11934,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>170</v>
       </c>
@@ -11716,7 +11956,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>170</v>
       </c>
@@ -11738,7 +11978,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>170</v>
       </c>
@@ -11760,7 +12000,7 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
         <v>170</v>
       </c>
@@ -11782,7 +12022,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>170</v>
       </c>
@@ -11804,7 +12044,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>170</v>
       </c>
@@ -11826,7 +12066,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
         <v>188</v>
       </c>
@@ -11840,7 +12080,7 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>188</v>
       </c>
@@ -11862,7 +12102,7 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>188</v>
       </c>
@@ -11884,7 +12124,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>188</v>
       </c>
@@ -11906,7 +12146,7 @@
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>188</v>
       </c>
@@ -11928,7 +12168,7 @@
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>188</v>
       </c>
@@ -11950,7 +12190,7 @@
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
         <v>188</v>
       </c>
@@ -11972,7 +12212,7 @@
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>188</v>
       </c>
@@ -11994,7 +12234,7 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
         <v>188</v>
       </c>
@@ -12016,7 +12256,7 @@
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>206</v>
       </c>
@@ -12030,7 +12270,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>206</v>
       </c>
@@ -12052,7 +12292,7 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="13" t="s">
         <v>210</v>
       </c>
@@ -12066,7 +12306,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>210</v>
       </c>
@@ -12088,7 +12328,7 @@
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="s">
         <v>210</v>
       </c>
@@ -12110,7 +12350,7 @@
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>210</v>
       </c>
@@ -12132,7 +12372,7 @@
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="19" t="s">
         <v>210</v>
       </c>
@@ -12154,7 +12394,7 @@
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>210</v>
       </c>
@@ -12202,7 +12442,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -12214,7 +12454,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -12240,7 +12480,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>222</v>
       </c>
@@ -12254,7 +12494,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>222</v>
       </c>
@@ -12276,7 +12516,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>222</v>
       </c>
@@ -12298,7 +12538,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>222</v>
       </c>
@@ -12320,7 +12560,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>222</v>
       </c>
@@ -12342,7 +12582,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>222</v>
       </c>
@@ -12364,7 +12604,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>234</v>
       </c>
@@ -12378,7 +12618,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>234</v>
       </c>
@@ -12400,7 +12640,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>234</v>
       </c>
@@ -12422,7 +12662,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>234</v>
       </c>
@@ -12444,7 +12684,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>234</v>
       </c>
@@ -12466,7 +12706,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>234</v>
       </c>
@@ -12488,7 +12728,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>246</v>
       </c>
@@ -12502,7 +12742,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>246</v>
       </c>
@@ -12524,7 +12764,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>246</v>
       </c>
@@ -12546,7 +12786,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>252</v>
       </c>
@@ -12560,7 +12800,7 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>252</v>
       </c>
@@ -12582,7 +12822,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>252</v>
       </c>
@@ -12604,7 +12844,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>252</v>
       </c>
@@ -12626,7 +12866,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>252</v>
       </c>
@@ -12674,7 +12914,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -12686,7 +12926,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -12712,7 +12952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>262</v>
       </c>
@@ -12726,7 +12966,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>262</v>
       </c>
@@ -12748,7 +12988,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>266</v>
       </c>
@@ -12762,7 +13002,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>266</v>
       </c>
@@ -12784,7 +13024,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>266</v>
       </c>
@@ -12806,7 +13046,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>266</v>
       </c>
@@ -12828,7 +13068,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>266</v>
       </c>
@@ -12850,7 +13090,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>266</v>
       </c>
@@ -12872,7 +13112,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>266</v>
       </c>
@@ -12894,7 +13134,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>280</v>
       </c>
@@ -12908,7 +13148,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>280</v>
       </c>
@@ -12930,7 +13170,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>280</v>
       </c>
@@ -12952,7 +13192,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>280</v>
       </c>
@@ -12974,7 +13214,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>288</v>
       </c>
@@ -12988,7 +13228,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>288</v>
       </c>
@@ -13010,7 +13250,7 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>288</v>
       </c>
@@ -13032,7 +13272,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>288</v>
       </c>
@@ -13080,7 +13320,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H56"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -13092,7 +13332,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -13118,7 +13358,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>296</v>
       </c>
@@ -13132,7 +13372,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>296</v>
       </c>
@@ -13154,7 +13394,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>296</v>
       </c>
@@ -13176,7 +13416,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>296</v>
       </c>
@@ -13198,7 +13438,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>304</v>
       </c>
@@ -13212,7 +13452,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>304</v>
       </c>
@@ -13238,7 +13478,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>304</v>
       </c>
@@ -13264,7 +13504,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>304</v>
       </c>
@@ -13290,7 +13530,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>304</v>
       </c>
@@ -13312,7 +13552,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>304</v>
       </c>
@@ -13334,7 +13574,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>304</v>
       </c>
@@ -13356,7 +13596,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>304</v>
       </c>
@@ -13378,7 +13618,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>304</v>
       </c>
@@ -13399,7 +13639,7 @@
       </c>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>304</v>
       </c>
@@ -13425,7 +13665,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>304</v>
       </c>
@@ -13449,7 +13689,7 @@
       </c>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>304</v>
       </c>
@@ -13475,7 +13715,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>304</v>
       </c>
@@ -13501,7 +13741,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>330</v>
       </c>
@@ -13515,7 +13755,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>330</v>
       </c>
@@ -13537,7 +13777,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>330</v>
       </c>
@@ -13559,7 +13799,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>330</v>
       </c>
@@ -13581,7 +13821,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>330</v>
       </c>
@@ -13603,7 +13843,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>330</v>
       </c>
@@ -13625,7 +13865,7 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>330</v>
       </c>
@@ -13647,7 +13887,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>330</v>
       </c>
@@ -13669,7 +13909,7 @@
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>330</v>
       </c>
@@ -13691,7 +13931,7 @@
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
         <v>348</v>
       </c>
@@ -13705,7 +13945,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>348</v>
       </c>
@@ -13727,7 +13967,7 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
         <v>348</v>
       </c>
@@ -13749,7 +13989,7 @@
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>348</v>
       </c>
@@ -13771,7 +14011,7 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
         <v>348</v>
       </c>
@@ -13793,7 +14033,7 @@
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>348</v>
       </c>
@@ -13815,7 +14055,7 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
         <v>348</v>
       </c>
@@ -13837,7 +14077,7 @@
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="13" t="s">
         <v>362</v>
       </c>
@@ -13851,7 +14091,7 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
         <v>362</v>
       </c>
@@ -13873,7 +14113,7 @@
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19" t="s">
         <v>362</v>
       </c>
@@ -13895,7 +14135,7 @@
       <c r="G37" s="21"/>
       <c r="H37" s="21"/>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>362</v>
       </c>
@@ -13917,7 +14157,7 @@
       <c r="G38" s="16"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="19" t="s">
         <v>362</v>
       </c>
@@ -13939,7 +14179,7 @@
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>362</v>
       </c>
@@ -13961,7 +14201,7 @@
       <c r="G40" s="16"/>
       <c r="H40" s="16"/>
     </row>
-    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="19" t="s">
         <v>362</v>
       </c>
@@ -13983,7 +14223,7 @@
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
         <v>362</v>
       </c>
@@ -14005,7 +14245,7 @@
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="19" t="s">
         <v>362</v>
       </c>
@@ -14027,7 +14267,7 @@
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
         <v>380</v>
       </c>
@@ -14041,7 +14281,7 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
     </row>
-    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>380</v>
       </c>
@@ -14063,7 +14303,7 @@
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="19" t="s">
         <v>380</v>
       </c>
@@ -14085,7 +14325,7 @@
       <c r="G46" s="21"/>
       <c r="H46" s="21"/>
     </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
         <v>380</v>
       </c>
@@ -14107,7 +14347,7 @@
       <c r="G47" s="16"/>
       <c r="H47" s="16"/>
     </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="19" t="s">
         <v>380</v>
       </c>
@@ -14129,7 +14369,7 @@
       <c r="G48" s="21"/>
       <c r="H48" s="21"/>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13" t="s">
         <v>390</v>
       </c>
@@ -14143,7 +14383,7 @@
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
     </row>
-    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
         <v>390</v>
       </c>
@@ -14165,7 +14405,7 @@
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="19" t="s">
         <v>390</v>
       </c>
@@ -14187,7 +14427,7 @@
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
         <v>396</v>
       </c>
@@ -14201,7 +14441,7 @@
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
     </row>
-    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
         <v>396</v>
       </c>
@@ -14223,7 +14463,7 @@
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
     </row>
-    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="19" t="s">
         <v>396</v>
       </c>
@@ -14245,7 +14485,7 @@
       <c r="G54" s="21"/>
       <c r="H54" s="21"/>
     </row>
-    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="14" t="s">
         <v>396</v>
       </c>
@@ -14267,7 +14507,7 @@
       <c r="G55" s="16"/>
       <c r="H55" s="16"/>
     </row>
-    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="19" t="s">
         <v>396</v>
       </c>
@@ -14320,7 +14560,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -14332,7 +14572,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -14358,7 +14598,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>406</v>
       </c>
@@ -14372,7 +14612,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>406</v>
       </c>
@@ -14394,7 +14634,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>406</v>
       </c>
@@ -14416,7 +14656,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>406</v>
       </c>
@@ -14438,7 +14678,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>414</v>
       </c>
@@ -14452,7 +14692,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>414</v>
       </c>
@@ -14478,7 +14718,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>414</v>
       </c>
@@ -14507,7 +14747,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>414</v>
       </c>
@@ -14529,7 +14769,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>414</v>
       </c>
@@ -14551,7 +14791,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>424</v>
       </c>
@@ -14565,7 +14805,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>424</v>
       </c>
@@ -14587,7 +14827,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>424</v>
       </c>
@@ -14613,7 +14853,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>430</v>
       </c>
@@ -14627,7 +14867,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>430</v>
       </c>
@@ -14653,7 +14893,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>430</v>
       </c>
@@ -14675,7 +14915,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>430</v>
       </c>
@@ -14697,7 +14937,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>430</v>
       </c>
@@ -14719,7 +14959,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>430</v>
       </c>
@@ -14741,7 +14981,7 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
         <v>442</v>
       </c>
@@ -14755,7 +14995,7 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>442</v>
       </c>
@@ -14777,7 +15017,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>442</v>
       </c>
@@ -14799,7 +15039,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>442</v>
       </c>
@@ -14821,7 +15061,7 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>450</v>
       </c>
@@ -14835,7 +15075,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>450</v>
       </c>
@@ -14857,7 +15097,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>450</v>
       </c>
@@ -14912,7 +15152,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -14924,7 +15164,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -14950,7 +15190,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>456</v>
       </c>
@@ -14964,7 +15204,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>456</v>
       </c>
@@ -14986,7 +15226,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>456</v>
       </c>
@@ -15008,7 +15248,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>456</v>
       </c>
@@ -15030,7 +15270,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>456</v>
       </c>
@@ -15052,7 +15292,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>466</v>
       </c>
@@ -15066,7 +15306,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>466</v>
       </c>
@@ -15092,7 +15332,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>466</v>
       </c>
@@ -15114,7 +15354,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>466</v>
       </c>
@@ -15136,7 +15376,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>466</v>
       </c>
@@ -15158,7 +15398,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>476</v>
       </c>
@@ -15172,7 +15412,7 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>476</v>
       </c>
@@ -15194,7 +15434,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>476</v>
       </c>
@@ -15216,7 +15456,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>476</v>
       </c>
@@ -15238,7 +15478,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>484</v>
       </c>
@@ -15252,7 +15492,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>484</v>
       </c>
@@ -15274,7 +15514,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>484</v>
       </c>

--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85DB334-B03A-4C87-B5F6-2A37DF57900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294FFC32-95D0-4FCC-986F-38B5C4A50360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="770" yWindow="740" windowWidth="14400" windowHeight="7270" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="969">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2960,6 +2960,18 @@
   </si>
   <si>
     <t>Requirements.md - NFR-01, NFR-02, NFR-05, Section 3 (BR-01 to BR-06)</t>
+  </si>
+  <si>
+    <t>Authentication protection controls are documented, including rate limiting requirements for sensitive endpoints such as login and registration.</t>
+  </si>
+  <si>
+    <t>Requirements.md - NFR-8</t>
+  </si>
+  <si>
+    <t>A context-specific password policy is documented. It defines that commonly used passwords and application-specific terms must not be accepted during registration or password change operations.</t>
+  </si>
+  <si>
+    <t>Requirements.md - BR-07 Password Policy</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3460,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.23076923076923078</c:v>
+                  <c:v>0.30769230769230771</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.5</c:v>
@@ -3632,7 +3644,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.18181818181818182</c:v>
+                  <c:v>0.22727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>8.3333333333333329E-2</c:v>
@@ -3997,7 +4009,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.14893617021276595</c:v>
+                  <c:v>0.19148936170212766</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.21052631578947367</c:v>
@@ -4896,22 +4908,22 @@
       </c>
       <c r="D11" s="7">
         <f>COUNTIFS('V6 - Authentication'!$F$2:$F$56,"Compliant",'V6 - Authentication'!$E$2:$E$56,1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="F11" s="7">
         <v>22</v>
       </c>
       <c r="G11" s="7">
         <f>COUNTIFS('V6 - Authentication'!$F$2:$F$56,"Compliant",'V6 - Authentication'!$E$2:$E$56,2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="I11" s="7">
         <v>12</v>
@@ -4926,11 +4938,11 @@
       </c>
       <c r="L11" s="7">
         <f>COUNTIF('V6 - Authentication'!$F$2:$F$56,"Compliant")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="3"/>
-        <v>0.14893617021276595</v>
+        <v>0.19148936170212766</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5480,11 +5492,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>0.17094017094017094</v>
+        <v>0.17606837606837605</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5492,11 +5504,11 @@
       </c>
       <c r="G23" s="10">
         <f>SUM(G6:G22)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="11">
         <f>IFERROR(AVERAGE(H6:H22),"")</f>
-        <v>0.10759184056397678</v>
+        <v>0.11026563735542062</v>
       </c>
       <c r="I23" s="10">
         <f>SUM(I6:I22)</f>
@@ -5512,11 +5524,11 @@
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>0.10398798937268075</v>
+        <v>0.10649111828381967</v>
       </c>
     </row>
   </sheetData>
@@ -13389,10 +13401,14 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>965</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -13411,10 +13427,14 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>967</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">

--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\OneDrive\Ambiente de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294FFC32-95D0-4FCC-986F-38B5C4A50360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F67A8-43FA-4AE3-AF46-CF961B15182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="770" yWindow="740" windowWidth="14400" windowHeight="7270" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="972">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2972,6 +2972,15 @@
   </si>
   <si>
     <t>Requirements.md - BR-07 Password Policy</t>
+  </si>
+  <si>
+    <t>Passwords are validated against compromised password databases using Have I Been Pwned integration and are also checked against application-specific forbidden terms.</t>
+  </si>
+  <si>
+    <t>The application enforces password length and blacklist validation but does not restrict the character composition of passwords.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/8eac90d29c53f3f94c5afe7d0e70417f54ea3fd0/TeaShop/TeaShop/Presentation/AuthController.cs</t>
   </si>
 </sst>
 </file>
@@ -3460,7 +3469,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.30769230769230771</c:v>
+                  <c:v>0.46153846153846156</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.5</c:v>
@@ -4009,7 +4018,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.19148936170212766</c:v>
+                  <c:v>0.23404255319148937</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.21052631578947367</c:v>
@@ -4908,11 +4917,11 @@
       </c>
       <c r="D11" s="7">
         <f>COUNTIFS('V6 - Authentication'!$F$2:$F$56,"Compliant",'V6 - Authentication'!$E$2:$E$56,1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="F11" s="7">
         <v>22</v>
@@ -4938,11 +4947,11 @@
       </c>
       <c r="L11" s="7">
         <f>COUNTIF('V6 - Authentication'!$F$2:$F$56,"Compliant")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="3"/>
-        <v>0.19148936170212766</v>
+        <v>0.23404255319148937</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5492,11 +5501,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>0.17606837606837605</v>
+        <v>0.18632478632478636</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5524,11 +5533,11 @@
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>0.10649111828381967</v>
+        <v>0.10899424719495861</v>
       </c>
     </row>
   </sheetData>
@@ -13546,7 +13555,7 @@
       <c r="G9" s="16" t="s">
         <v>904</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="24" t="s">
         <v>897</v>
       </c>
     </row>
@@ -13567,10 +13576,14 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
@@ -13589,10 +13602,14 @@
         <v>1</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
@@ -14571,6 +14588,9 @@
     <hyperlink ref="H7" r:id="rId1" location="L21" xr:uid="{F596CCA9-524A-46C7-9C77-F6EA6F450E91}"/>
     <hyperlink ref="H8" r:id="rId2" location="L52" xr:uid="{65E8B584-A00F-4884-A727-264FF99EB138}"/>
     <hyperlink ref="H18" r:id="rId3" location="L27" xr:uid="{E112FC84-77A3-41FD-92F9-0CF4A1D171BE}"/>
+    <hyperlink ref="H9" r:id="rId4" location="L117" xr:uid="{91645EE2-7393-4503-92C1-CC7EA3162839}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{C370F1BE-887F-4566-9C70-1B36A846657C}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{2001B137-FFE0-4FB0-88EE-DCDC3C42F888}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\OneDrive\Ambiente de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85DB334-B03A-4C87-B5F6-2A37DF57900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F67A8-43FA-4AE3-AF46-CF961B15182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="972">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2960,6 +2960,27 @@
   </si>
   <si>
     <t>Requirements.md - NFR-01, NFR-02, NFR-05, Section 3 (BR-01 to BR-06)</t>
+  </si>
+  <si>
+    <t>Authentication protection controls are documented, including rate limiting requirements for sensitive endpoints such as login and registration.</t>
+  </si>
+  <si>
+    <t>Requirements.md - NFR-8</t>
+  </si>
+  <si>
+    <t>A context-specific password policy is documented. It defines that commonly used passwords and application-specific terms must not be accepted during registration or password change operations.</t>
+  </si>
+  <si>
+    <t>Requirements.md - BR-07 Password Policy</t>
+  </si>
+  <si>
+    <t>Passwords are validated against compromised password databases using Have I Been Pwned integration and are also checked against application-specific forbidden terms.</t>
+  </si>
+  <si>
+    <t>The application enforces password length and blacklist validation but does not restrict the character composition of passwords.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/8eac90d29c53f3f94c5afe7d0e70417f54ea3fd0/TeaShop/TeaShop/Presentation/AuthController.cs</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3469,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.23076923076923078</c:v>
+                  <c:v>0.46153846153846156</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.5</c:v>
@@ -3632,7 +3653,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.18181818181818182</c:v>
+                  <c:v>0.22727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>8.3333333333333329E-2</c:v>
@@ -3997,7 +4018,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.14893617021276595</c:v>
+                  <c:v>0.23404255319148937</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.21052631578947367</c:v>
@@ -4896,22 +4917,22 @@
       </c>
       <c r="D11" s="7">
         <f>COUNTIFS('V6 - Authentication'!$F$2:$F$56,"Compliant",'V6 - Authentication'!$E$2:$E$56,1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="F11" s="7">
         <v>22</v>
       </c>
       <c r="G11" s="7">
         <f>COUNTIFS('V6 - Authentication'!$F$2:$F$56,"Compliant",'V6 - Authentication'!$E$2:$E$56,2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="I11" s="7">
         <v>12</v>
@@ -4926,11 +4947,11 @@
       </c>
       <c r="L11" s="7">
         <f>COUNTIF('V6 - Authentication'!$F$2:$F$56,"Compliant")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="3"/>
-        <v>0.14893617021276595</v>
+        <v>0.23404255319148937</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5480,11 +5501,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>0.17094017094017094</v>
+        <v>0.18632478632478636</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5492,11 +5513,11 @@
       </c>
       <c r="G23" s="10">
         <f>SUM(G6:G22)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="11">
         <f>IFERROR(AVERAGE(H6:H22),"")</f>
-        <v>0.10759184056397678</v>
+        <v>0.11026563735542062</v>
       </c>
       <c r="I23" s="10">
         <f>SUM(I6:I22)</f>
@@ -5512,11 +5533,11 @@
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>0.10398798937268075</v>
+        <v>0.10899424719495861</v>
       </c>
     </row>
   </sheetData>
@@ -13389,10 +13410,14 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>965</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -13411,10 +13436,14 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>967</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
@@ -13526,7 +13555,7 @@
       <c r="G9" s="16" t="s">
         <v>904</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="24" t="s">
         <v>897</v>
       </c>
     </row>
@@ -13547,10 +13576,14 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
@@ -13569,10 +13602,14 @@
         <v>1</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
@@ -14551,6 +14588,9 @@
     <hyperlink ref="H7" r:id="rId1" location="L21" xr:uid="{F596CCA9-524A-46C7-9C77-F6EA6F450E91}"/>
     <hyperlink ref="H8" r:id="rId2" location="L52" xr:uid="{65E8B584-A00F-4884-A727-264FF99EB138}"/>
     <hyperlink ref="H18" r:id="rId3" location="L27" xr:uid="{E112FC84-77A3-41FD-92F9-0CF4A1D171BE}"/>
+    <hyperlink ref="H9" r:id="rId4" location="L117" xr:uid="{91645EE2-7393-4503-92C1-CC7EA3162839}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{C370F1BE-887F-4566-9C70-1B36A846657C}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{2001B137-FFE0-4FB0-88EE-DCDC3C42F888}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
+++ b/Deliverables/Sprint_1/ASVS_5.0_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\OneDrive\Ambiente de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\desofs2026-tue_crr_3\Deliverables\Sprint_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F67A8-43FA-4AE3-AF46-CF961B15182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A18B02A-1DCA-49CB-A964-3FFC7620539C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="15" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="1051">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2981,6 +2981,243 @@
   </si>
   <si>
     <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/8eac90d29c53f3f94c5afe7d0e70417f54ea3fd0/TeaShop/TeaShop/Presentation/AuthController.cs</t>
+  </si>
+  <si>
+    <t>We enforce authorization at the controller layer using ASP.NET Core's `[Authorize]` attribute with policy-based checks before any business logic is executed.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Presentation/OrderController.cs#L90</t>
+  </si>
+  <si>
+    <t>Resource ownership is verified at the domain level before allowing state changes like cancellations.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Domain/Orders/Order.cs#L39</t>
+  </si>
+  <si>
+    <t>README 1.1 section</t>
+  </si>
+  <si>
+    <t>The project repository  (README) includes an authorization table mapping user roles to endpoints</t>
+  </si>
+  <si>
+    <t>Token expiration is enforced on the server-side session object via `session.IsValid()` in the IAMMiddleware.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Infrastructure/Middleware/IAMMiddleware.cs#L33</t>
+  </si>
+  <si>
+    <t>The application prevents token type confusion by isolating session tokens in a dedicated database store accessed via `ISessionRepository`. The authentication middleware (`IAMMiddleware`) strictly validates that incoming bearer tokens resolve to active, unrevoked user session entities</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Infrastructure/Middleware/IAMMiddleware.cs#L22</t>
+  </si>
+  <si>
+    <t>The application uses standard, industry-validated .NET framework libraries (`System.Security.Cryptography`) and Microsoft Identity packages, completely avoiding custom cryptography</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Domain/IAM/SessionToken.cs#L1</t>
+  </si>
+  <si>
+    <t>All cryptographic primitives meet or exceed 128-bit security; session tokens utilize 256-bit (32-byte) entropy, and password hashing uses PBKDF2 with SHA-256</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Domain/IAM/SessionToken.cs#L14</t>
+  </si>
+  <si>
+    <t>Cryptographic agility is achieved through encapsulation. Token generation is isolated within the `SessionToken` domain class, allowing algorithm updates without modifying application services. Password hashing relies on the framework's default abstraction (`IPasswordHasher`), which automatically manages algorithm upgrades and iteration increases</t>
+  </si>
+  <si>
+    <t>User passwords are hashed and stored using PBKDF2 with HMAC-SHA256, which is an approved key derivation function managed natively by the Microsoft.AspNetCore.Identity package.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/0ac8ba6aa386181a974b76a3e9347de8cdb8000e/TeaShop/TeaShop/Infrastructure/Security/PasswordHashingService.cs#L1</t>
+  </si>
+  <si>
+    <t>Non-guessable session tokens are generated using the .NET framework's 'RandomNumberGenerator.GetBytes' CSPRNG, ensuring maximum entropy</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Deployment/nginx.conf#L27</t>
+  </si>
+  <si>
+    <t>TLS 1.0 and 1.1 are disabled at the reverse-proxy layer.Only TLS 1.2 and TLS 1.3 are enabled for traffic encryption.</t>
+  </si>
+  <si>
+    <t>The reverse-proxy/hosting environment is configured to negotiate only strong, industry-recommended cipher suites</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Deployment/nginx.conf#L28</t>
+  </si>
+  <si>
+    <t>The application redirects all HTTP requests to HTTPS using `app.UseHttpsRedirection()`, and enforces HTTP Strict Transport Security (HSTS) via `app.UseHsts()` in production to prevent downgrade attacks</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Program.cs#L97</t>
+  </si>
+  <si>
+    <t>All inbound traffic is encrypted via the Nginx reverse proxy over HTTPS. Any outbound API integrations are restricted strictly to secure TLS (`https://`) endpoints</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Deployment/nginx.conf#L1</t>
+  </si>
+  <si>
+    <t>he C# backend relies on default .NET `HttpClient` behavior, which automatically validates remote server certificates and rejects untrusted or expired certificates</t>
+  </si>
+  <si>
+    <t>Standard .NET framework behavior</t>
+  </si>
+  <si>
+    <t>The application has no features that accept user-supplied URLs for backend fetching, completely eliminating Server-Side Request Forgery risk.</t>
+  </si>
+  <si>
+    <t>he DB connection string is loaded dynamically from configuration with SSL/TLS validation enabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Docker environments, the connection string is injected via `.env` while Local development uses uncommitted .NET User Secrets.</t>
+  </si>
+  <si>
+    <t>In Docker environments, the credentials are injected via `.env` while Local development uses uncommitted .NET User Secrets.</t>
+  </si>
+  <si>
+    <t>Access to secrets adheres to least privilege; the database password is only injected into the C# backend container and is isolated from the Nginx reverse proxy and other infrastructure components</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Deployment/docker-compose.yml#L12</t>
+  </si>
+  <si>
+    <t>HALF COMPLIANT,while  All secrets are excluded from the source code and build artifacts no management solution is being used only .env and secret files</t>
+  </si>
+  <si>
+    <t>"The Docker multi-stage build copy only includes compiled assets from `dotnet publish`. A `.dockerignore` file prevents `.git` metadata from entering the build context.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/.dockerignore#L1</t>
+  </si>
+  <si>
+    <t>Directory browsing is disabled by default in ASP.NET Core and is not enabled in the program</t>
+  </si>
+  <si>
+    <t>The HTTP TRACE method is not supported or mapped by the Kestrel web server routing configuration</t>
+  </si>
+  <si>
+    <t>Standard .NET behavior</t>
+  </si>
+  <si>
+    <t>Swagger UI and OpenAPI endpoints  are explicitly wrapped in environment checks so they are never exposed in production</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Program.cs#L88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debug logging for production via `appsettings.Production.json` logging configuration is restricted to  `Warning` </t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/appsettings.json#L16</t>
+  </si>
+  <si>
+    <t>Sensitive data (such as passwords and session tokens) is never transmitted in URLs or query strings. Passwords are sent in JSON request bodies, and session tokens are transmitted strictly via the HTTP `Authorization` header.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Infrastructure/Middleware/IAMMiddleware.cs#L42</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Program.cs#L81</t>
+  </si>
+  <si>
+    <t>The backend API is entirely self-contained and does not integrate with any third-party telemetry, marketing trackers, or analytics scripts</t>
+  </si>
+  <si>
+    <t>The application utilizes the 'AddDefaultSecurityHeaders()' middleware, which automatically injects strict cache-control headers  to prevent intermediate caching proxies and CDNs from caching sensitive API responses</t>
+  </si>
+  <si>
+    <t>The application utilizes the 'AddDefaultSecurityHeaders()' middleware, which automatically injects strict cache-control headers  to prevent browsers  from caching sensitive API responses</t>
+  </si>
+  <si>
+    <t>Application dependencies  are audited for vulnerabilities and kept up to date using NuGet Audit during the build phase and automated dependency monitoring (such as GitHub Dependabot)</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Infrastructure/Security/RateLimiting.cs#L1</t>
+  </si>
+  <si>
+    <t>The application implements rate limiting middleware  configured with custom policies  to prevent brute-force and Denial of Service (DoS) attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dockerfile compiles the code in 'Release' mode, which strips debugging configurations,  Swagger UI, OpenAPI schemas, and development exception pages are completely excluded from the production  pipeline and Test are a different project that is seperated from the program</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Program.cs#L2</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Dockerfile#L18</t>
+  </si>
+  <si>
+    <t>The application utilizes explicit Data Transfer Objects (such as `OrderDto`) to ensure only a safe, required subset of database entity fields is returned</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Application/Orders/OrderDTOs.cs#L14</t>
+  </si>
+  <si>
+    <t>Mass assignment is prevented by binding incoming controller requests to dedicated request models.</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Application/Orders/OrderDTOs.cs#L28</t>
+  </si>
+  <si>
+    <t>The application configures `ForwardedHeadersOptions` in production to safely extract proxy IP headers, explicitly restricting trust to pre-configured known IP networks</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Program.cs#L32</t>
+  </si>
+  <si>
+    <t>The backend is written in C#, a strongly-typed language that enforces strict type safety at compile-time and prevents implicit type coercion bugs.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core's model binding engine automatically resolves duplicate query or route parameters safely when mapping to strongly-typed action parameters</t>
+  </si>
+  <si>
+    <t>add dependency injection link after commit</t>
+  </si>
+  <si>
+    <t>The application's outbound HTTP client configures 'AllowAutoRedirect = false' to prevent redirect exploitation</t>
+  </si>
+  <si>
+    <t>The built-in .NET logging engine automatically includes critical metadata for every event,</t>
+  </si>
+  <si>
+    <t>All timestamps are written strictly in UTC format by the Kestrel web serve</t>
+  </si>
+  <si>
+    <t>The application outputs structured logs containing .NET's native W3C Trace Context</t>
+  </si>
+  <si>
+    <t>To protect sensitive data,  passwords and credentials are never logged,  custom session tokens are strictly excluded from logging statements.The only instance of credential logged is email which is hashed before being logged</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Application/Auth/AuthService.cs#L72</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Application/Auth/AuthService.cs#L96</t>
+  </si>
+  <si>
+    <t>Unexpected exceptions are caught globally by 'GenericExceptionMiddleware'</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Infrastructure/Middleware/GenericExceptionMiddleware.cs#L31</t>
+  </si>
+  <si>
+    <t>Failed authorization decisions  requiring the  are automatically logged as Warnings by ASP.NET Core's authorization middleware and preserved by our production log level filters</t>
+  </si>
+  <si>
+    <t>The system logs authentication events. Unsuccessful attempts  are captured on the server, and the custom `IAMMiddleware` explicitly logs a security warning for invalid session requests</t>
+  </si>
+  <si>
+    <t>The application actively prevents log injection by sanitizing the data before logging</t>
+  </si>
+  <si>
+    <t>https://github.com/mei-desofs/desofs2026-tue_crr_3/blob/badde573ec6ab2a7ea7a6d911606cd9cedccc851/TeaShop/TeaShop/Application/Products/CategoryService.cs#L107</t>
+  </si>
+  <si>
+    <t>The application logs to two documented destinations: standard console output  and rolling local files</t>
   </si>
 </sst>
 </file>
@@ -3318,7 +3555,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3475,10 +3712,10 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.25</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3487,16 +3724,16 @@
                   <c:v>0.33333333333333331</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.66666666666666663</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.66666666666666663</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
                   <c:v>0</c:v>
@@ -3662,28 +3899,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.33333333333333331</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.45454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.14285714285714285</c:v>
+                  <c:v>0.5714285714285714</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.5625</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -4024,31 +4261,31 @@
                   <c:v>0.21052631578947367</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>0.30769230769230771</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.2857142857142857</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.1666666666666664E-2</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.41666666666666669</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.47619047619047616</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>0.38461538461538464</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.38095238095238093</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.52941176470588236</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -4564,13 +4801,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -4590,7 +4827,7 @@
       <c r="O1" s="28"/>
       <c r="P1" s="28"/>
     </row>
-    <row r="2" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29"/>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4608,7 +4845,7 @@
       <c r="O2" s="29"/>
       <c r="P2" s="29"/>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
       <c r="B3" s="30"/>
       <c r="C3" s="1"/>
@@ -4619,7 +4856,7 @@
       <c r="M3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -4660,7 +4897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -4709,7 +4946,7 @@
         <v>0.36666666666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
@@ -4758,7 +4995,7 @@
         <v>0.84615384615384615</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -4807,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -4856,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -4905,7 +5142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -4954,7 +5191,7 @@
         <v>0.23404255319148937</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -5003,7 +5240,7 @@
         <v>0.21052631578947367</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -5015,11 +5252,11 @@
       </c>
       <c r="D13" s="7">
         <f>COUNTIFS('V8 - Authorization'!$F$2:$F$18,"Compliant",'V8 - Authorization'!$E$2:$E$18,1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7">
         <v>3</v>
@@ -5045,14 +5282,14 @@
       </c>
       <c r="L13" s="7">
         <f>COUNTIF('V8 - Authorization'!$F$2:$F$18,"Compliant")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="3"/>
-        <v>7.6923076923076927E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.30769230769230771</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -5064,22 +5301,22 @@
       </c>
       <c r="D14" s="4">
         <f>COUNTIFS('V9 - Self-contained Tokens'!$F$2:$F$10,"Compliant",'V9 - Self-contained Tokens'!$E$2:$E$10,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="4">
         <v>3</v>
       </c>
       <c r="G14" s="4">
         <f>COUNTIFS('V9 - Self-contained Tokens'!$F$2:$F$10,"Compliant",'V9 - Self-contained Tokens'!$E$2:$E$10,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -5092,14 +5329,14 @@
       </c>
       <c r="L14" s="4">
         <f>COUNTIF('V9 - Self-contained Tokens'!$F$2:$F$10,"Compliant")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -5148,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -5171,11 +5408,11 @@
       </c>
       <c r="G16" s="4">
         <f>COUNTIFS('V11 - Cryptography'!$F$2:$F$32,"Compliant",'V11 - Cryptography'!$E$2:$E$32,2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="I16" s="4">
         <v>10</v>
@@ -5190,14 +5427,14 @@
       </c>
       <c r="L16" s="4">
         <f>COUNTIF('V11 - Cryptography'!$F$2:$F$32,"Compliant")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M16" s="5">
         <f t="shared" si="3"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>26</v>
       </c>
@@ -5209,22 +5446,22 @@
       </c>
       <c r="D17" s="7">
         <f>COUNTIFS('V12 - Secure Communication'!$F$2:$F$16,"Compliant",'V12 - Secure Communication'!$E$2:$E$16,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F17" s="7">
         <v>6</v>
       </c>
       <c r="G17" s="7">
         <f>COUNTIFS('V12 - Secure Communication'!$F$2:$F$16,"Compliant",'V12 - Secure Communication'!$E$2:$E$16,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="7">
         <v>3</v>
@@ -5239,14 +5476,14 @@
       </c>
       <c r="L17" s="7">
         <f>COUNTIF('V12 - Secure Communication'!$F$2:$F$16,"Compliant")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -5258,22 +5495,22 @@
       </c>
       <c r="D18" s="4">
         <f>COUNTIFS('V13 - Configuration'!$F$2:$F$26,"Compliant",'V13 - Configuration'!$E$2:$E$26,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4">
         <v>12</v>
       </c>
       <c r="G18" s="4">
         <f>COUNTIFS('V13 - Configuration'!$F$2:$F$26,"Compliant",'V13 - Configuration'!$E$2:$E$26,2)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H18" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I18" s="4">
         <v>8</v>
@@ -5288,14 +5525,14 @@
       </c>
       <c r="L18" s="4">
         <f>COUNTIF('V13 - Configuration'!$F$2:$F$26,"Compliant")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M18" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.47619047619047616</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>28</v>
       </c>
@@ -5307,22 +5544,22 @@
       </c>
       <c r="D19" s="7">
         <f>COUNTIFS('V14 - Data Protection'!$F$2:$F$17,"Compliant",'V14 - Data Protection'!$E$2:$E$17,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="7">
         <v>7</v>
       </c>
       <c r="G19" s="7">
         <f>COUNTIFS('V14 - Data Protection'!$F$2:$F$17,"Compliant",'V14 - Data Protection'!$E$2:$E$17,2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I19" s="7">
         <v>4</v>
@@ -5337,14 +5574,14 @@
       </c>
       <c r="L19" s="7">
         <f>COUNTIF('V14 - Data Protection'!$F$2:$F$17,"Compliant")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="3"/>
-        <v>7.6923076923076927E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.38461538461538464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -5356,22 +5593,22 @@
       </c>
       <c r="D20" s="4">
         <f>COUNTIFS('V15 - Secure Coding and Archite'!$F$2:$F$26,"Compliant",'V15 - Secure Coding and Archite'!$E$2:$E$26,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F20" s="4">
         <v>10</v>
       </c>
       <c r="G20" s="4">
         <f>COUNTIFS('V15 - Secure Coding and Archite'!$F$2:$F$26,"Compliant",'V15 - Secure Coding and Archite'!$E$2:$E$26,2)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="4">
         <v>8</v>
@@ -5386,14 +5623,14 @@
       </c>
       <c r="L20" s="4">
         <f>COUNTIF('V15 - Secure Coding and Archite'!$F$2:$F$26,"Compliant")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M20" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.38095238095238093</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
@@ -5414,11 +5651,11 @@
       </c>
       <c r="G21" s="7">
         <f>COUNTIFS('V16 - Security Logging and Erro'!$F$2:$F$23,"Compliant",'V16 - Security Logging and Erro'!$E$2:$E$23,2)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="I21" s="7">
         <v>1</v>
@@ -5433,14 +5670,14 @@
       </c>
       <c r="L21" s="7">
         <f>COUNTIF('V16 - Security Logging and Erro'!$F$2:$F$23,"Compliant")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.52941176470588236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -5487,7 +5724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -5501,11 +5738,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUM(D6:D22)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E23" s="11">
         <f>IFERROR(AVERAGE(E6:E22),"")</f>
-        <v>0.18632478632478636</v>
+        <v>0.44188034188034192</v>
       </c>
       <c r="F23" s="10">
         <f>SUM(F6:F22)</f>
@@ -5513,11 +5750,11 @@
       </c>
       <c r="G23" s="10">
         <f>SUM(G6:G22)</f>
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="H23" s="11">
         <f>IFERROR(AVERAGE(H6:H22),"")</f>
-        <v>0.11026563735542062</v>
+        <v>0.32373329714660981</v>
       </c>
       <c r="I23" s="10">
         <f>SUM(I6:I22)</f>
@@ -5533,11 +5770,11 @@
       </c>
       <c r="L23" s="10">
         <f>SUM(L6:L22)</f>
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="M23" s="11">
         <f>IFERROR(AVERAGE(M6:M22),"")</f>
-        <v>0.10899424719495861</v>
+        <v>0.27580192049052116</v>
       </c>
     </row>
   </sheetData>
@@ -5603,7 +5840,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5615,7 +5852,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -5641,7 +5878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>490</v>
       </c>
@@ -5655,7 +5892,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>490</v>
       </c>
@@ -5672,12 +5909,12 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>490</v>
       </c>
@@ -5694,12 +5931,12 @@
         <v>1</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>490</v>
       </c>
@@ -5716,12 +5953,12 @@
         <v>1</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>498</v>
       </c>
@@ -5735,7 +5972,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>498</v>
       </c>
@@ -5752,12 +5989,16 @@
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>978</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>498</v>
       </c>
@@ -5774,12 +6015,16 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>980</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>498</v>
       </c>
@@ -5796,12 +6041,12 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>498</v>
       </c>
@@ -5818,7 +6063,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
@@ -5841,6 +6086,10 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H7" r:id="rId1" location="L33" xr:uid="{4C574203-FCE6-4E9E-85CD-D0AE9F6BDA94}"/>
+    <hyperlink ref="H8" r:id="rId2" location="L22" xr:uid="{0712BE8B-A94B-49BE-8B0A-2378BC9380F0}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5849,7 +6098,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5861,7 +6110,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -5887,7 +6136,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>508</v>
       </c>
@@ -5901,7 +6150,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>508</v>
       </c>
@@ -5918,12 +6167,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>508</v>
       </c>
@@ -5940,12 +6189,12 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>514</v>
       </c>
@@ -5959,7 +6208,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>514</v>
       </c>
@@ -5976,12 +6225,12 @@
         <v>2</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>514</v>
       </c>
@@ -5998,12 +6247,12 @@
         <v>2</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>514</v>
       </c>
@@ -6020,12 +6269,12 @@
         <v>3</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>522</v>
       </c>
@@ -6039,7 +6288,7 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>522</v>
       </c>
@@ -6056,12 +6305,12 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>522</v>
       </c>
@@ -6078,12 +6327,12 @@
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>522</v>
       </c>
@@ -6100,12 +6349,12 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>522</v>
       </c>
@@ -6122,12 +6371,12 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>522</v>
       </c>
@@ -6144,12 +6393,12 @@
         <v>3</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>534</v>
       </c>
@@ -6163,7 +6412,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>534</v>
       </c>
@@ -6180,12 +6429,12 @@
         <v>1</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>534</v>
       </c>
@@ -6202,12 +6451,12 @@
         <v>1</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>534</v>
       </c>
@@ -6224,12 +6473,12 @@
         <v>1</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>534</v>
       </c>
@@ -6246,12 +6495,12 @@
         <v>1</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>534</v>
       </c>
@@ -6268,12 +6517,12 @@
         <v>1</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>534</v>
       </c>
@@ -6290,12 +6539,12 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>534</v>
       </c>
@@ -6312,12 +6561,12 @@
         <v>2</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>534</v>
       </c>
@@ -6334,12 +6583,12 @@
         <v>2</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>534</v>
       </c>
@@ -6356,12 +6605,12 @@
         <v>2</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>534</v>
       </c>
@@ -6378,12 +6627,12 @@
         <v>2</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>534</v>
       </c>
@@ -6400,12 +6649,12 @@
         <v>2</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>534</v>
       </c>
@@ -6422,12 +6671,12 @@
         <v>3</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>534</v>
       </c>
@@ -6444,12 +6693,12 @@
         <v>3</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>534</v>
       </c>
@@ -6466,12 +6715,12 @@
         <v>3</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>534</v>
       </c>
@@ -6488,12 +6737,12 @@
         <v>3</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>534</v>
       </c>
@@ -6510,12 +6759,12 @@
         <v>3</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>568</v>
       </c>
@@ -6529,7 +6778,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>568</v>
       </c>
@@ -6546,12 +6795,12 @@
         <v>2</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>568</v>
       </c>
@@ -6568,12 +6817,12 @@
         <v>2</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>568</v>
       </c>
@@ -6590,12 +6839,12 @@
         <v>2</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>568</v>
       </c>
@@ -6612,12 +6861,12 @@
         <v>2</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>568</v>
       </c>
@@ -6634,12 +6883,12 @@
         <v>2</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>580</v>
       </c>
@@ -6653,7 +6902,7 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>580</v>
       </c>
@@ -6670,12 +6919,12 @@
         <v>2</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G39" s="16"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>580</v>
       </c>
@@ -6692,12 +6941,12 @@
         <v>2</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>586</v>
       </c>
@@ -6711,7 +6960,7 @@
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>586</v>
       </c>
@@ -6728,12 +6977,12 @@
         <v>2</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>586</v>
       </c>
@@ -6750,12 +6999,12 @@
         <v>2</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
     </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>586</v>
       </c>
@@ -6772,7 +7021,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G44" s="16"/>
       <c r="H44" s="16"/>
@@ -6803,7 +7052,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -6815,7 +7064,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -6841,7 +7090,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>594</v>
       </c>
@@ -6855,7 +7104,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>594</v>
       </c>
@@ -6877,7 +7126,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>594</v>
       </c>
@@ -6899,7 +7148,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>594</v>
       </c>
@@ -6916,12 +7165,12 @@
         <v>3</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>594</v>
       </c>
@@ -6938,12 +7187,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>604</v>
       </c>
@@ -6957,7 +7206,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>604</v>
       </c>
@@ -6974,12 +7223,16 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>604</v>
       </c>
@@ -6996,12 +7249,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>986</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>604</v>
       </c>
@@ -7018,12 +7275,16 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>984</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>604</v>
       </c>
@@ -7040,12 +7301,12 @@
         <v>3</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>604</v>
       </c>
@@ -7062,12 +7323,12 @@
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>616</v>
       </c>
@@ -7081,7 +7342,7 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>616</v>
       </c>
@@ -7098,12 +7359,12 @@
         <v>1</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>616</v>
       </c>
@@ -7120,12 +7381,12 @@
         <v>1</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>616</v>
       </c>
@@ -7142,12 +7403,12 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>616</v>
       </c>
@@ -7164,12 +7425,12 @@
         <v>3</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>616</v>
       </c>
@@ -7186,12 +7447,12 @@
         <v>3</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>628</v>
       </c>
@@ -7205,7 +7466,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>628</v>
       </c>
@@ -7231,7 +7492,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>628</v>
       </c>
@@ -7248,12 +7509,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>987</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>628</v>
       </c>
@@ -7270,12 +7535,12 @@
         <v>2</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>628</v>
       </c>
@@ -7292,12 +7557,12 @@
         <v>2</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>638</v>
       </c>
@@ -7311,7 +7576,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>638</v>
       </c>
@@ -7328,12 +7593,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>989</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>638</v>
       </c>
@@ -7350,12 +7619,12 @@
         <v>3</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>644</v>
       </c>
@@ -7369,7 +7638,7 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>644</v>
       </c>
@@ -7386,12 +7655,12 @@
         <v>2</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>644</v>
       </c>
@@ -7408,12 +7677,12 @@
         <v>3</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>650</v>
       </c>
@@ -7427,7 +7696,7 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>650</v>
       </c>
@@ -7444,12 +7713,12 @@
         <v>3</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>650</v>
       </c>
@@ -7466,7 +7735,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
@@ -7491,6 +7760,10 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H20" r:id="rId1" location="L1" xr:uid="{4CEB0538-09C9-484B-86F6-761C19E93F10}"/>
+    <hyperlink ref="H10" r:id="rId2" location="L14" xr:uid="{E196AE93-05CC-484D-A493-3E2291BA0EC9}"/>
+    <hyperlink ref="H9" r:id="rId3" location="L1" xr:uid="{67850970-FEE1-459B-B86B-7D9F4462693C}"/>
+    <hyperlink ref="H21" r:id="rId4" location="L1" xr:uid="{CAC31737-63E2-4430-A74B-E6ABDBBBDA05}"/>
+    <hyperlink ref="H25" r:id="rId5" location="L14" xr:uid="{B86EA74C-B49C-4087-93F7-789E7FA37BA4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7500,7 +7773,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -7512,7 +7785,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -7538,7 +7811,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>656</v>
       </c>
@@ -7552,7 +7825,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>656</v>
       </c>
@@ -7569,12 +7842,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>656</v>
       </c>
@@ -7591,12 +7868,16 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>992</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>656</v>
       </c>
@@ -7613,12 +7894,12 @@
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>656</v>
       </c>
@@ -7635,12 +7916,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>656</v>
       </c>
@@ -7657,12 +7938,12 @@
         <v>3</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>668</v>
       </c>
@@ -7676,7 +7957,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>668</v>
       </c>
@@ -7693,12 +7974,16 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>668</v>
       </c>
@@ -7715,12 +8000,12 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>674</v>
       </c>
@@ -7734,7 +8019,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>674</v>
       </c>
@@ -7751,12 +8036,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>674</v>
       </c>
@@ -7773,12 +8062,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-    </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>998</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>674</v>
       </c>
@@ -7795,12 +8088,12 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>674</v>
       </c>
@@ -7817,12 +8110,12 @@
         <v>2</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>674</v>
       </c>
@@ -7839,7 +8132,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -7862,6 +8155,12 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" location="L28" xr:uid="{8F2A7CBA-FEB4-4DE4-907B-1F9EA8F40526}"/>
+    <hyperlink ref="H3" r:id="rId2" location="L27" xr:uid="{C42BDE2F-738D-42AC-9E1D-01E42D6B9F75}"/>
+    <hyperlink ref="H9" r:id="rId3" location="L97" xr:uid="{07C4F8E1-8A3B-444D-B2AD-4D9F25ECEBC3}"/>
+    <hyperlink ref="H12" r:id="rId4" location="L1" xr:uid="{8ACD0795-2E30-40DD-A3D2-DF70FC17BF5D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -7870,7 +8169,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -7882,7 +8181,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -7908,7 +8207,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>686</v>
       </c>
@@ -7922,7 +8221,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>686</v>
       </c>
@@ -7944,7 +8243,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>686</v>
       </c>
@@ -7961,12 +8260,12 @@
         <v>3</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>686</v>
       </c>
@@ -7983,12 +8282,12 @@
         <v>3</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>686</v>
       </c>
@@ -8005,12 +8304,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>696</v>
       </c>
@@ -8024,7 +8323,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>696</v>
       </c>
@@ -8041,12 +8340,12 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>696</v>
       </c>
@@ -8063,12 +8362,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>696</v>
       </c>
@@ -8085,12 +8388,14 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>892</v>
       </c>
       <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H10" s="16" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>696</v>
       </c>
@@ -8112,7 +8417,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>696</v>
       </c>
@@ -8129,12 +8434,14 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1000</v>
+      </c>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>696</v>
       </c>
@@ -8151,12 +8458,12 @@
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>710</v>
       </c>
@@ -8170,7 +8477,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>710</v>
       </c>
@@ -8187,12 +8494,14 @@
         <v>2</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1006</v>
+      </c>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>710</v>
       </c>
@@ -8209,12 +8518,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>710</v>
       </c>
@@ -8231,12 +8544,12 @@
         <v>3</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>710</v>
       </c>
@@ -8253,12 +8566,12 @@
         <v>3</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>720</v>
       </c>
@@ -8272,7 +8585,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>720</v>
       </c>
@@ -8289,12 +8602,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>720</v>
       </c>
@@ -8311,12 +8628,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>720</v>
       </c>
@@ -8333,12 +8654,14 @@
         <v>2</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>1009</v>
+      </c>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>720</v>
       </c>
@@ -8355,12 +8678,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>720</v>
       </c>
@@ -8377,12 +8704,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>720</v>
       </c>
@@ -8399,12 +8730,12 @@
         <v>3</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>720</v>
       </c>
@@ -8421,7 +8752,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
@@ -8444,6 +8775,12 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" r:id="rId1" location="L12" xr:uid="{B01FBCCF-E6D5-4130-BCC4-AE3E32CC73DE}"/>
+    <hyperlink ref="H20" r:id="rId2" location="L1" xr:uid="{525C3C8A-4F5D-487A-9C0D-CE3E360B8936}"/>
+    <hyperlink ref="H24" r:id="rId3" location="L88" xr:uid="{CA576D13-EA1E-4108-B0AD-7D5C68D9FC5B}"/>
+    <hyperlink ref="H21" r:id="rId4" location="L16" xr:uid="{5F1F73BE-C79E-495F-978D-D8A8B0C692B6}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -8452,7 +8789,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8464,7 +8801,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -8490,7 +8827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>736</v>
       </c>
@@ -8504,7 +8841,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>736</v>
       </c>
@@ -8530,7 +8867,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>736</v>
       </c>
@@ -8552,7 +8889,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>742</v>
       </c>
@@ -8566,7 +8903,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>742</v>
       </c>
@@ -8583,12 +8920,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>742</v>
       </c>
@@ -8605,12 +8946,16 @@
         <v>2</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>742</v>
       </c>
@@ -8627,12 +8972,14 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>1019</v>
+      </c>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>742</v>
       </c>
@@ -8654,7 +9001,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>742</v>
       </c>
@@ -8671,12 +9018,12 @@
         <v>3</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>742</v>
       </c>
@@ -8693,12 +9040,12 @@
         <v>3</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>742</v>
       </c>
@@ -8715,12 +9062,12 @@
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>742</v>
       </c>
@@ -8737,12 +9084,12 @@
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>760</v>
       </c>
@@ -8756,7 +9103,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>760</v>
       </c>
@@ -8773,12 +9120,12 @@
         <v>1</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>760</v>
       </c>
@@ -8795,12 +9142,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>760</v>
       </c>
@@ -8817,7 +9168,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
@@ -8842,6 +9193,9 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" location="L136" xr:uid="{60DC742D-9B3F-4C18-A91A-E26E15765FCE}"/>
+    <hyperlink ref="H6" r:id="rId2" location="L42" xr:uid="{DA412250-58BF-4EBE-B8F8-84ABEAE665C2}"/>
+    <hyperlink ref="H7" r:id="rId3" location="L81" xr:uid="{29EC24D4-BA6D-43ED-B8BF-7D322D6416CF}"/>
+    <hyperlink ref="H16" r:id="rId4" location="L81" xr:uid="{658BA6DA-AAED-4111-BEB1-8890C07D8999}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8850,8 +9204,8 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8863,7 +9217,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -8889,7 +9243,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>768</v>
       </c>
@@ -8903,7 +9257,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>768</v>
       </c>
@@ -8925,7 +9279,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>768</v>
       </c>
@@ -8947,7 +9301,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>768</v>
       </c>
@@ -8969,7 +9323,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>768</v>
       </c>
@@ -8986,12 +9340,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>768</v>
       </c>
@@ -9008,12 +9362,12 @@
         <v>3</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>780</v>
       </c>
@@ -9027,7 +9381,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>780</v>
       </c>
@@ -9044,12 +9398,14 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1022</v>
+      </c>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>780</v>
       </c>
@@ -9066,12 +9422,16 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>780</v>
       </c>
@@ -9090,10 +9450,17 @@
       <c r="F11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G11" s="16" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>780</v>
       </c>
@@ -9110,12 +9477,12 @@
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>780</v>
       </c>
@@ -9132,12 +9499,12 @@
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>792</v>
       </c>
@@ -9151,7 +9518,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>792</v>
       </c>
@@ -9168,12 +9535,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>792</v>
       </c>
@@ -9190,12 +9561,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>792</v>
       </c>
@@ -9212,12 +9587,16 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>792</v>
       </c>
@@ -9234,12 +9613,16 @@
         <v>2</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-    </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>792</v>
       </c>
@@ -9256,12 +9639,14 @@
         <v>2</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1034</v>
+      </c>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>792</v>
       </c>
@@ -9278,12 +9663,12 @@
         <v>2</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>792</v>
       </c>
@@ -9300,12 +9685,14 @@
         <v>2</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1035</v>
+      </c>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>808</v>
       </c>
@@ -9319,7 +9706,7 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>808</v>
       </c>
@@ -9336,12 +9723,12 @@
         <v>3</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>808</v>
       </c>
@@ -9358,12 +9745,12 @@
         <v>3</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>808</v>
       </c>
@@ -9380,12 +9767,12 @@
         <v>3</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>808</v>
       </c>
@@ -9402,7 +9789,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
@@ -9425,6 +9812,14 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H10" r:id="rId1" location="L1" xr:uid="{79EA020E-779F-4D1F-BA91-BDF08D8833C7}"/>
+    <hyperlink ref="H11" r:id="rId2" location="L2" xr:uid="{42F92FB6-AD7F-48EC-B8CE-83DED212C2E4}"/>
+    <hyperlink ref="I11" r:id="rId3" location="L18" xr:uid="{B78AF4DA-213F-4EE9-A202-176DDB2C41D3}"/>
+    <hyperlink ref="H15" r:id="rId4" location="L14" xr:uid="{A4997E43-15FF-4826-B9EF-0B4F37B6FE49}"/>
+    <hyperlink ref="H17" r:id="rId5" location="L28" xr:uid="{2C1FB71F-CA47-4BD0-8AA3-55EA971E75ED}"/>
+    <hyperlink ref="H18" r:id="rId6" location="L32" xr:uid="{AAC80AC0-C50A-4131-9A0E-197E26278C15}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9433,7 +9828,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -9445,7 +9840,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -9471,7 +9866,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>818</v>
       </c>
@@ -9485,7 +9880,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>818</v>
       </c>
@@ -9507,7 +9902,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>822</v>
       </c>
@@ -9521,7 +9916,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>822</v>
       </c>
@@ -9538,12 +9933,14 @@
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1038</v>
+      </c>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>822</v>
       </c>
@@ -9560,12 +9957,14 @@
         <v>2</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>1039</v>
+      </c>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>822</v>
       </c>
@@ -9582,12 +9981,14 @@
         <v>2</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16"/>
+        <v>892</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1050</v>
+      </c>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>822</v>
       </c>
@@ -9604,12 +10005,14 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>1040</v>
+      </c>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>822</v>
       </c>
@@ -9626,12 +10029,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>834</v>
       </c>
@@ -9645,7 +10052,7 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>834</v>
       </c>
@@ -9662,12 +10069,16 @@
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>834</v>
       </c>
@@ -9684,12 +10095,14 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="21"/>
+        <v>892</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>1046</v>
+      </c>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>834</v>
       </c>
@@ -9711,7 +10124,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>834</v>
       </c>
@@ -9728,12 +10141,16 @@
         <v>2</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>844</v>
       </c>
@@ -9747,7 +10164,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>844</v>
       </c>
@@ -9764,12 +10181,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>844</v>
       </c>
@@ -9791,7 +10212,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>844</v>
       </c>
@@ -9813,7 +10234,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>852</v>
       </c>
@@ -9827,7 +10248,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>852</v>
       </c>
@@ -9849,7 +10270,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>852</v>
       </c>
@@ -9871,7 +10292,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>852</v>
       </c>
@@ -9893,7 +10314,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>852</v>
       </c>
@@ -9910,7 +10331,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
@@ -9933,6 +10354,12 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H9" r:id="rId1" location="L72" xr:uid="{492B3198-4DD8-4BD3-897D-624A76A87E58}"/>
+    <hyperlink ref="H11" r:id="rId2" location="L96" xr:uid="{68A7A85C-45AC-44D2-8CC7-044FAE7B4710}"/>
+    <hyperlink ref="H14" r:id="rId3" location="L31" xr:uid="{181A30D7-DF8E-495F-AC4F-956BCC86E518}"/>
+    <hyperlink ref="H16" r:id="rId4" location="L107" xr:uid="{7F389C9C-8381-411F-A841-D8660179DEB0}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9941,7 +10368,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -9953,7 +10380,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -9979,7 +10406,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>862</v>
       </c>
@@ -9993,7 +10420,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>862</v>
       </c>
@@ -10010,12 +10437,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>862</v>
       </c>
@@ -10032,12 +10459,12 @@
         <v>3</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>868</v>
       </c>
@@ -10051,7 +10478,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>868</v>
       </c>
@@ -10068,12 +10495,12 @@
         <v>2</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>868</v>
       </c>
@@ -10090,12 +10517,12 @@
         <v>2</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>868</v>
       </c>
@@ -10112,12 +10539,12 @@
         <v>2</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>868</v>
       </c>
@@ -10134,12 +10561,12 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>868</v>
       </c>
@@ -10156,12 +10583,12 @@
         <v>3</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>868</v>
       </c>
@@ -10178,12 +10605,12 @@
         <v>3</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>868</v>
       </c>
@@ -10200,12 +10627,12 @@
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>868</v>
       </c>
@@ -10222,12 +10649,12 @@
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>886</v>
       </c>
@@ -10241,7 +10668,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>886</v>
       </c>
@@ -10258,12 +10685,12 @@
         <v>2</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>886</v>
       </c>
@@ -10280,7 +10707,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
@@ -10311,7 +10738,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -10323,7 +10750,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -10349,7 +10776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>41</v>
       </c>
@@ -10363,7 +10790,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>41</v>
       </c>
@@ -10389,7 +10816,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>41</v>
       </c>
@@ -10415,7 +10842,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -10429,7 +10856,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>48</v>
       </c>
@@ -10451,7 +10878,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>48</v>
       </c>
@@ -10473,7 +10900,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>48</v>
       </c>
@@ -10499,7 +10926,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>48</v>
       </c>
@@ -10525,7 +10952,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>48</v>
       </c>
@@ -10547,7 +10974,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>48</v>
       </c>
@@ -10569,7 +10996,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>48</v>
       </c>
@@ -10591,7 +11018,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>48</v>
       </c>
@@ -10613,7 +11040,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>48</v>
       </c>
@@ -10635,7 +11062,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>48</v>
       </c>
@@ -10661,7 +11088,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>70</v>
       </c>
@@ -10675,7 +11102,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>70</v>
       </c>
@@ -10697,7 +11124,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>70</v>
       </c>
@@ -10719,7 +11146,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -10745,7 +11172,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>70</v>
       </c>
@@ -10767,7 +11194,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -10789,7 +11216,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>70</v>
       </c>
@@ -10811,7 +11238,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -10833,7 +11260,7 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>70</v>
       </c>
@@ -10855,7 +11282,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>70</v>
       </c>
@@ -10877,7 +11304,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>70</v>
       </c>
@@ -10903,7 +11330,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>70</v>
       </c>
@@ -10925,7 +11352,7 @@
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>70</v>
       </c>
@@ -10947,7 +11374,7 @@
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>96</v>
       </c>
@@ -10961,7 +11388,7 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>96</v>
       </c>
@@ -10985,7 +11412,7 @@
       </c>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>96</v>
       </c>
@@ -11011,7 +11438,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>96</v>
       </c>
@@ -11037,7 +11464,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>104</v>
       </c>
@@ -11051,7 +11478,7 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>104</v>
       </c>
@@ -11073,7 +11500,7 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>104</v>
       </c>
@@ -11099,7 +11526,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>104</v>
       </c>
@@ -11157,7 +11584,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -11169,7 +11596,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -11195,7 +11622,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>112</v>
       </c>
@@ -11209,7 +11636,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>112</v>
       </c>
@@ -11235,7 +11662,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>112</v>
       </c>
@@ -11261,7 +11688,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>112</v>
       </c>
@@ -11287,7 +11714,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>120</v>
       </c>
@@ -11301,7 +11728,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>120</v>
       </c>
@@ -11327,7 +11754,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>120</v>
       </c>
@@ -11353,7 +11780,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>120</v>
       </c>
@@ -11379,7 +11806,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>128</v>
       </c>
@@ -11393,7 +11820,7 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>128</v>
       </c>
@@ -11419,7 +11846,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>128</v>
       </c>
@@ -11445,7 +11872,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>128</v>
       </c>
@@ -11471,7 +11898,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>128</v>
       </c>
@@ -11497,7 +11924,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>128</v>
       </c>
@@ -11519,7 +11946,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>140</v>
       </c>
@@ -11533,7 +11960,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>140</v>
       </c>
@@ -11562,7 +11989,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>140</v>
       </c>
@@ -11619,7 +12046,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -11631,7 +12058,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -11657,7 +12084,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>146</v>
       </c>
@@ -11671,7 +12098,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
@@ -11688,12 +12115,12 @@
         <v>3</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>150</v>
       </c>
@@ -11707,7 +12134,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>150</v>
       </c>
@@ -11724,12 +12151,12 @@
         <v>1</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>150</v>
       </c>
@@ -11746,12 +12173,12 @@
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>150</v>
       </c>
@@ -11768,12 +12195,12 @@
         <v>3</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>158</v>
       </c>
@@ -11787,7 +12214,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>158</v>
       </c>
@@ -11804,12 +12231,12 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>158</v>
       </c>
@@ -11826,12 +12253,12 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>158</v>
       </c>
@@ -11848,12 +12275,12 @@
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>158</v>
       </c>
@@ -11870,12 +12297,12 @@
         <v>2</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>158</v>
       </c>
@@ -11892,12 +12319,12 @@
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>170</v>
       </c>
@@ -11911,7 +12338,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>170</v>
       </c>
@@ -11928,12 +12355,12 @@
         <v>1</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>170</v>
       </c>
@@ -11950,12 +12377,12 @@
         <v>1</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>170</v>
       </c>
@@ -11972,12 +12399,12 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>170</v>
       </c>
@@ -11994,12 +12421,12 @@
         <v>2</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>170</v>
       </c>
@@ -12016,12 +12443,12 @@
         <v>2</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>170</v>
       </c>
@@ -12038,12 +12465,12 @@
         <v>2</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>170</v>
       </c>
@@ -12060,12 +12487,12 @@
         <v>3</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>170</v>
       </c>
@@ -12082,12 +12509,12 @@
         <v>3</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>188</v>
       </c>
@@ -12101,7 +12528,7 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>188</v>
       </c>
@@ -12118,12 +12545,12 @@
         <v>1</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>188</v>
       </c>
@@ -12140,12 +12567,12 @@
         <v>1</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>188</v>
       </c>
@@ -12162,12 +12589,12 @@
         <v>1</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>188</v>
       </c>
@@ -12184,12 +12611,12 @@
         <v>2</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>188</v>
       </c>
@@ -12206,12 +12633,12 @@
         <v>2</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>188</v>
       </c>
@@ -12228,12 +12655,12 @@
         <v>3</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>188</v>
       </c>
@@ -12250,12 +12677,12 @@
         <v>3</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>188</v>
       </c>
@@ -12272,12 +12699,12 @@
         <v>3</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>206</v>
       </c>
@@ -12291,7 +12718,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>206</v>
       </c>
@@ -12308,12 +12735,12 @@
         <v>3</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>210</v>
       </c>
@@ -12327,7 +12754,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>210</v>
       </c>
@@ -12344,12 +12771,12 @@
         <v>2</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>210</v>
       </c>
@@ -12366,12 +12793,12 @@
         <v>2</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>210</v>
       </c>
@@ -12388,12 +12815,12 @@
         <v>3</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>210</v>
       </c>
@@ -12410,12 +12837,12 @@
         <v>3</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>210</v>
       </c>
@@ -12432,7 +12859,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G39" s="16"/>
       <c r="H39" s="16"/>
@@ -12463,7 +12890,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -12475,7 +12902,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -12501,7 +12928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>222</v>
       </c>
@@ -12515,7 +12942,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>222</v>
       </c>
@@ -12537,7 +12964,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>222</v>
       </c>
@@ -12559,7 +12986,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>222</v>
       </c>
@@ -12581,7 +13008,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>222</v>
       </c>
@@ -12603,7 +13030,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>222</v>
       </c>
@@ -12625,7 +13052,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>234</v>
       </c>
@@ -12639,7 +13066,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>234</v>
       </c>
@@ -12661,7 +13088,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>234</v>
       </c>
@@ -12683,7 +13110,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>234</v>
       </c>
@@ -12705,7 +13132,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>234</v>
       </c>
@@ -12727,7 +13154,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>234</v>
       </c>
@@ -12749,7 +13176,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>246</v>
       </c>
@@ -12763,7 +13190,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>246</v>
       </c>
@@ -12785,7 +13212,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>246</v>
       </c>
@@ -12807,7 +13234,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>252</v>
       </c>
@@ -12821,7 +13248,7 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>252</v>
       </c>
@@ -12843,7 +13270,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>252</v>
       </c>
@@ -12865,7 +13292,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>252</v>
       </c>
@@ -12887,7 +13314,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>252</v>
       </c>
@@ -12935,7 +13362,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -12947,7 +13374,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -12973,7 +13400,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>262</v>
       </c>
@@ -12987,7 +13414,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>262</v>
       </c>
@@ -13009,7 +13436,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>266</v>
       </c>
@@ -13023,7 +13450,7 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>266</v>
       </c>
@@ -13045,7 +13472,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>266</v>
       </c>
@@ -13067,7 +13494,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>266</v>
       </c>
@@ -13089,7 +13516,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>266</v>
       </c>
@@ -13111,7 +13538,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>266</v>
       </c>
@@ -13133,7 +13560,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>266</v>
       </c>
@@ -13155,7 +13582,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>280</v>
       </c>
@@ -13169,7 +13596,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>280</v>
       </c>
@@ -13191,7 +13618,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>280</v>
       </c>
@@ -13213,7 +13640,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>280</v>
       </c>
@@ -13235,7 +13662,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>288</v>
       </c>
@@ -13249,7 +13676,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>288</v>
       </c>
@@ -13271,7 +13698,7 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>288</v>
       </c>
@@ -13293,7 +13720,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>288</v>
       </c>
@@ -13341,7 +13768,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H56"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -13353,7 +13780,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -13379,7 +13806,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>296</v>
       </c>
@@ -13393,7 +13820,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>296</v>
       </c>
@@ -13419,7 +13846,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>296</v>
       </c>
@@ -13445,7 +13872,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>296</v>
       </c>
@@ -13467,7 +13894,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>304</v>
       </c>
@@ -13481,7 +13908,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>304</v>
       </c>
@@ -13507,7 +13934,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>304</v>
       </c>
@@ -13533,7 +13960,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>304</v>
       </c>
@@ -13559,7 +13986,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>304</v>
       </c>
@@ -13585,7 +14012,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>304</v>
       </c>
@@ -13611,7 +14038,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>304</v>
       </c>
@@ -13633,7 +14060,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>304</v>
       </c>
@@ -13655,7 +14082,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>304</v>
       </c>
@@ -13676,7 +14103,7 @@
       </c>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>304</v>
       </c>
@@ -13702,7 +14129,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>304</v>
       </c>
@@ -13726,7 +14153,7 @@
       </c>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>304</v>
       </c>
@@ -13752,7 +14179,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>304</v>
       </c>
@@ -13778,7 +14205,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>330</v>
       </c>
@@ -13792,7 +14219,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>330</v>
       </c>
@@ -13814,7 +14241,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>330</v>
       </c>
@@ -13836,7 +14263,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>330</v>
       </c>
@@ -13858,7 +14285,7 @@
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>330</v>
       </c>
@@ -13880,7 +14307,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>330</v>
       </c>
@@ -13902,7 +14329,7 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>330</v>
       </c>
@@ -13924,7 +14351,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>330</v>
       </c>
@@ -13946,7 +14373,7 @@
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>330</v>
       </c>
@@ -13968,7 +14395,7 @@
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>348</v>
       </c>
@@ -13982,7 +14409,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>348</v>
       </c>
@@ -14004,7 +14431,7 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>348</v>
       </c>
@@ -14026,7 +14453,7 @@
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>348</v>
       </c>
@@ -14048,7 +14475,7 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>348</v>
       </c>
@@ -14070,7 +14497,7 @@
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>348</v>
       </c>
@@ -14092,7 +14519,7 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>348</v>
       </c>
@@ -14114,7 +14541,7 @@
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>362</v>
       </c>
@@ -14128,7 +14555,7 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>362</v>
       </c>
@@ -14150,7 +14577,7 @@
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>362</v>
       </c>
@@ -14172,7 +14599,7 @@
       <c r="G37" s="21"/>
       <c r="H37" s="21"/>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>362</v>
       </c>
@@ -14194,7 +14621,7 @@
       <c r="G38" s="16"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
         <v>362</v>
       </c>
@@ -14216,7 +14643,7 @@
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>362</v>
       </c>
@@ -14238,7 +14665,7 @@
       <c r="G40" s="16"/>
       <c r="H40" s="16"/>
     </row>
-    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>362</v>
       </c>
@@ -14260,7 +14687,7 @@
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>362</v>
       </c>
@@ -14282,7 +14709,7 @@
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>362</v>
       </c>
@@ -14304,7 +14731,7 @@
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>380</v>
       </c>
@@ -14318,7 +14745,7 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
     </row>
-    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>380</v>
       </c>
@@ -14340,7 +14767,7 @@
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>380</v>
       </c>
@@ -14362,7 +14789,7 @@
       <c r="G46" s="21"/>
       <c r="H46" s="21"/>
     </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>380</v>
       </c>
@@ -14384,7 +14811,7 @@
       <c r="G47" s="16"/>
       <c r="H47" s="16"/>
     </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
         <v>380</v>
       </c>
@@ -14406,7 +14833,7 @@
       <c r="G48" s="21"/>
       <c r="H48" s="21"/>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>390</v>
       </c>
@@ -14420,7 +14847,7 @@
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
     </row>
-    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>390</v>
       </c>
@@ -14442,7 +14869,7 @@
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
         <v>390</v>
       </c>
@@ -14464,7 +14891,7 @@
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>396</v>
       </c>
@@ -14478,7 +14905,7 @@
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
     </row>
-    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>396</v>
       </c>
@@ -14500,7 +14927,7 @@
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
     </row>
-    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
         <v>396</v>
       </c>
@@ -14522,7 +14949,7 @@
       <c r="G54" s="21"/>
       <c r="H54" s="21"/>
     </row>
-    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>396</v>
       </c>
@@ -14544,7 +14971,7 @@
       <c r="G55" s="16"/>
       <c r="H55" s="16"/>
     </row>
-    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
         <v>396</v>
       </c>
@@ -14600,7 +15027,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -14612,7 +15039,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -14638,7 +15065,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>406</v>
       </c>
@@ -14652,7 +15079,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>406</v>
       </c>
@@ -14674,7 +15101,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>406</v>
       </c>
@@ -14696,7 +15123,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>406</v>
       </c>
@@ -14718,7 +15145,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>414</v>
       </c>
@@ -14732,7 +15159,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>414</v>
       </c>
@@ -14758,7 +15185,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>414</v>
       </c>
@@ -14787,7 +15214,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>414</v>
       </c>
@@ -14809,7 +15236,7 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>414</v>
       </c>
@@ -14831,7 +15258,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>424</v>
       </c>
@@ -14845,7 +15272,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>424</v>
       </c>
@@ -14867,7 +15294,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>424</v>
       </c>
@@ -14893,7 +15320,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>430</v>
       </c>
@@ -14907,7 +15334,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>430</v>
       </c>
@@ -14933,7 +15360,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>430</v>
       </c>
@@ -14955,7 +15382,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>430</v>
       </c>
@@ -14977,7 +15404,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>430</v>
       </c>
@@ -14999,7 +15426,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>430</v>
       </c>
@@ -15021,7 +15448,7 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>442</v>
       </c>
@@ -15035,7 +15462,7 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>442</v>
       </c>
@@ -15057,7 +15484,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>442</v>
       </c>
@@ -15079,7 +15506,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>442</v>
       </c>
@@ -15101,7 +15528,7 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>450</v>
       </c>
@@ -15115,7 +15542,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>450</v>
       </c>
@@ -15137,7 +15564,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>450</v>
       </c>
@@ -15192,7 +15619,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -15204,7 +15631,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
@@ -15230,7 +15657,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>456</v>
       </c>
@@ -15244,7 +15671,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>456</v>
       </c>
@@ -15261,12 +15688,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>977</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>456</v>
       </c>
@@ -15288,7 +15719,7 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>456</v>
       </c>
@@ -15305,12 +15736,12 @@
         <v>3</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>456</v>
       </c>
@@ -15327,12 +15758,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>466</v>
       </c>
@@ -15346,7 +15777,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>466</v>
       </c>
@@ -15372,7 +15803,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>466</v>
       </c>
@@ -15389,12 +15820,16 @@
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>974</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>466</v>
       </c>
@@ -15411,12 +15846,12 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>466</v>
       </c>
@@ -15433,12 +15868,12 @@
         <v>3</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>476</v>
       </c>
@@ -15452,7 +15887,7 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>476</v>
       </c>
@@ -15469,12 +15904,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>972</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>476</v>
       </c>
@@ -15491,12 +15930,12 @@
         <v>3</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>476</v>
       </c>
@@ -15513,12 +15952,12 @@
         <v>3</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>484</v>
       </c>
@@ -15532,7 +15971,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>484</v>
       </c>
@@ -15549,12 +15988,12 @@
         <v>2</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>484</v>
       </c>
@@ -15571,7 +16010,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>45</v>
+        <v>924</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
@@ -15596,6 +16035,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H8" r:id="rId1" location="L95" xr:uid="{ABFA394F-53FC-472E-B84B-2C70A0ADD836}"/>
+    <hyperlink ref="H13" r:id="rId2" location="L90" xr:uid="{3317B289-10D2-4962-95B9-029BE53966E7}"/>
+    <hyperlink ref="H9" r:id="rId3" location="L39" xr:uid="{E8666D7E-CAF3-40DF-8183-0EF33FC4D123}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
